--- a/xardas/main/templates/doc/chx-blank.xlsx
+++ b/xardas/main/templates/doc/chx-blank.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Страница 1" sheetId="1" state="visible" r:id="rId2"/>
@@ -569,364 +569,380 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="94">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1003,7 +1019,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -4318,8 +4334,8 @@
     <mergeCell ref="P50:S53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4328,7 +4344,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -7312,8 +7328,8 @@
     <mergeCell ref="U48:BA53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7322,7 +7338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -7777,317 +7793,408 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="79"/>
-      <c r="AN10" s="80"/>
-      <c r="AO10" s="80"/>
-      <c r="AP10" s="80"/>
-      <c r="AQ10" s="80"/>
-      <c r="AR10" s="80"/>
-      <c r="AS10" s="80"/>
-      <c r="AT10" s="80"/>
-      <c r="AU10" s="80"/>
-      <c r="AV10" s="80"/>
-      <c r="AW10" s="80"/>
-      <c r="AX10" s="80"/>
-      <c r="AY10" s="80"/>
-      <c r="AZ10" s="80"/>
+      <c r="AN10" s="82"/>
+      <c r="AO10" s="82"/>
+      <c r="AP10" s="82"/>
+      <c r="AQ10" s="82"/>
+      <c r="AR10" s="82"/>
+      <c r="AS10" s="82"/>
+      <c r="AT10" s="82"/>
+      <c r="AU10" s="82"/>
+      <c r="AV10" s="82"/>
+      <c r="AW10" s="82"/>
+      <c r="AX10" s="82"/>
+      <c r="AY10" s="82"/>
+      <c r="AZ10" s="82"/>
       <c r="BA10" s="81"/>
       <c r="BB10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="3"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="83"/>
-      <c r="O11" s="83"/>
-      <c r="P11" s="83"/>
-      <c r="Q11" s="84"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="84"/>
+      <c r="O11" s="84"/>
+      <c r="P11" s="84"/>
+      <c r="Q11" s="85"/>
       <c r="R11" s="2"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-      <c r="U11" s="82"/>
-      <c r="V11" s="83"/>
-      <c r="W11" s="83"/>
-      <c r="X11" s="83"/>
-      <c r="Y11" s="83"/>
-      <c r="Z11" s="83"/>
-      <c r="AA11" s="83"/>
-      <c r="AB11" s="83"/>
-      <c r="AC11" s="83"/>
-      <c r="AD11" s="83"/>
-      <c r="AE11" s="83"/>
-      <c r="AF11" s="83"/>
-      <c r="AG11" s="83"/>
-      <c r="AH11" s="83"/>
-      <c r="AI11" s="84"/>
+      <c r="U11" s="83"/>
+      <c r="V11" s="84"/>
+      <c r="W11" s="84"/>
+      <c r="X11" s="84"/>
+      <c r="Y11" s="84"/>
+      <c r="Z11" s="84"/>
+      <c r="AA11" s="84"/>
+      <c r="AB11" s="84"/>
+      <c r="AC11" s="84"/>
+      <c r="AD11" s="84"/>
+      <c r="AE11" s="84"/>
+      <c r="AF11" s="84"/>
+      <c r="AG11" s="84"/>
+      <c r="AH11" s="84"/>
+      <c r="AI11" s="85"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
-      <c r="AM11" s="82"/>
-      <c r="AN11" s="83"/>
-      <c r="AO11" s="83"/>
-      <c r="AP11" s="83"/>
-      <c r="AQ11" s="83"/>
-      <c r="AR11" s="83"/>
-      <c r="AS11" s="83"/>
-      <c r="AT11" s="83"/>
-      <c r="AU11" s="83"/>
-      <c r="AV11" s="83"/>
-      <c r="AW11" s="83"/>
-      <c r="AX11" s="83"/>
-      <c r="AY11" s="83"/>
-      <c r="AZ11" s="83"/>
-      <c r="BA11" s="84"/>
+      <c r="AM11" s="83"/>
+      <c r="AN11" s="86"/>
+      <c r="AO11" s="86"/>
+      <c r="AP11" s="86"/>
+      <c r="AQ11" s="86"/>
+      <c r="AR11" s="86"/>
+      <c r="AS11" s="86"/>
+      <c r="AT11" s="86"/>
+      <c r="AU11" s="86"/>
+      <c r="AV11" s="86"/>
+      <c r="AW11" s="86"/>
+      <c r="AX11" s="86"/>
+      <c r="AY11" s="86"/>
+      <c r="AZ11" s="86"/>
+      <c r="BA11" s="85"/>
       <c r="BB11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="3"/>
-      <c r="C12" s="82"/>
-      <c r="Q12" s="84"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="87"/>
+      <c r="L12" s="87"/>
+      <c r="M12" s="87"/>
+      <c r="N12" s="87"/>
+      <c r="O12" s="87"/>
+      <c r="P12" s="87"/>
+      <c r="Q12" s="85"/>
       <c r="R12" s="2"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
-      <c r="U12" s="82"/>
-      <c r="AI12" s="84"/>
+      <c r="U12" s="83"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="87"/>
+      <c r="X12" s="87"/>
+      <c r="Y12" s="87"/>
+      <c r="Z12" s="87"/>
+      <c r="AA12" s="87"/>
+      <c r="AB12" s="87"/>
+      <c r="AC12" s="87"/>
+      <c r="AD12" s="87"/>
+      <c r="AE12" s="87"/>
+      <c r="AF12" s="87"/>
+      <c r="AG12" s="87"/>
+      <c r="AH12" s="87"/>
+      <c r="AI12" s="85"/>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
-      <c r="AM12" s="82"/>
-      <c r="BA12" s="84"/>
+      <c r="AM12" s="83"/>
+      <c r="BA12" s="85"/>
       <c r="BB12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="83"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="83"/>
-      <c r="Q13" s="84"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="84"/>
+      <c r="P13" s="84"/>
+      <c r="Q13" s="85"/>
       <c r="R13" s="2"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
-      <c r="U13" s="82"/>
-      <c r="V13" s="83"/>
-      <c r="W13" s="83"/>
-      <c r="X13" s="83"/>
-      <c r="Y13" s="83"/>
-      <c r="Z13" s="83"/>
-      <c r="AA13" s="83"/>
-      <c r="AB13" s="83"/>
-      <c r="AC13" s="83"/>
-      <c r="AD13" s="83"/>
-      <c r="AE13" s="83"/>
-      <c r="AF13" s="83"/>
-      <c r="AG13" s="83"/>
-      <c r="AH13" s="83"/>
-      <c r="AI13" s="84"/>
+      <c r="U13" s="83"/>
+      <c r="V13" s="84"/>
+      <c r="W13" s="84"/>
+      <c r="X13" s="84"/>
+      <c r="Y13" s="84"/>
+      <c r="Z13" s="84"/>
+      <c r="AA13" s="84"/>
+      <c r="AB13" s="84"/>
+      <c r="AC13" s="84"/>
+      <c r="AD13" s="84"/>
+      <c r="AE13" s="84"/>
+      <c r="AF13" s="84"/>
+      <c r="AG13" s="84"/>
+      <c r="AH13" s="84"/>
+      <c r="AI13" s="85"/>
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
-      <c r="AM13" s="82"/>
-      <c r="AN13" s="83"/>
-      <c r="AO13" s="83"/>
-      <c r="AP13" s="83"/>
-      <c r="AQ13" s="83"/>
-      <c r="AR13" s="83"/>
-      <c r="AS13" s="83"/>
-      <c r="AT13" s="83"/>
-      <c r="AU13" s="83"/>
-      <c r="AV13" s="83"/>
-      <c r="AW13" s="83"/>
-      <c r="AX13" s="83"/>
-      <c r="AY13" s="83"/>
-      <c r="AZ13" s="83"/>
-      <c r="BA13" s="84"/>
+      <c r="AM13" s="83"/>
+      <c r="AN13" s="86"/>
+      <c r="AO13" s="86"/>
+      <c r="AP13" s="86"/>
+      <c r="AQ13" s="86"/>
+      <c r="AR13" s="86"/>
+      <c r="AS13" s="86"/>
+      <c r="AT13" s="86"/>
+      <c r="AU13" s="86"/>
+      <c r="AV13" s="86"/>
+      <c r="AW13" s="86"/>
+      <c r="AX13" s="86"/>
+      <c r="AY13" s="86"/>
+      <c r="AZ13" s="86"/>
+      <c r="BA13" s="85"/>
       <c r="BB13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="3"/>
-      <c r="C14" s="82"/>
-      <c r="Q14" s="84"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87"/>
+      <c r="K14" s="87"/>
+      <c r="L14" s="87"/>
+      <c r="M14" s="87"/>
+      <c r="N14" s="87"/>
+      <c r="O14" s="87"/>
+      <c r="P14" s="87"/>
+      <c r="Q14" s="85"/>
       <c r="R14" s="2"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="82"/>
-      <c r="AI14" s="84"/>
+      <c r="U14" s="83"/>
+      <c r="V14" s="87"/>
+      <c r="W14" s="87"/>
+      <c r="X14" s="87"/>
+      <c r="Y14" s="87"/>
+      <c r="Z14" s="87"/>
+      <c r="AA14" s="87"/>
+      <c r="AB14" s="87"/>
+      <c r="AC14" s="87"/>
+      <c r="AD14" s="87"/>
+      <c r="AE14" s="87"/>
+      <c r="AF14" s="87"/>
+      <c r="AG14" s="87"/>
+      <c r="AH14" s="87"/>
+      <c r="AI14" s="85"/>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
-      <c r="AM14" s="82"/>
-      <c r="BA14" s="84"/>
+      <c r="AM14" s="83"/>
+      <c r="BA14" s="85"/>
       <c r="BB14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="3"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="83"/>
-      <c r="N15" s="83"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="83"/>
-      <c r="Q15" s="84"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="85"/>
       <c r="R15" s="2"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="82"/>
-      <c r="V15" s="83"/>
-      <c r="W15" s="83"/>
-      <c r="X15" s="83"/>
-      <c r="Y15" s="83"/>
-      <c r="Z15" s="83"/>
-      <c r="AA15" s="83"/>
-      <c r="AB15" s="83"/>
-      <c r="AC15" s="83"/>
-      <c r="AD15" s="83"/>
-      <c r="AE15" s="83"/>
-      <c r="AF15" s="83"/>
-      <c r="AG15" s="83"/>
-      <c r="AH15" s="83"/>
-      <c r="AI15" s="84"/>
+      <c r="U15" s="83"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="84"/>
+      <c r="AD15" s="84"/>
+      <c r="AE15" s="84"/>
+      <c r="AF15" s="84"/>
+      <c r="AG15" s="84"/>
+      <c r="AH15" s="84"/>
+      <c r="AI15" s="85"/>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
-      <c r="AM15" s="82"/>
-      <c r="AN15" s="83"/>
-      <c r="AO15" s="83"/>
-      <c r="AP15" s="83"/>
-      <c r="AQ15" s="83"/>
-      <c r="AR15" s="83"/>
-      <c r="AS15" s="83"/>
-      <c r="AT15" s="83"/>
-      <c r="AU15" s="83"/>
-      <c r="AV15" s="83"/>
-      <c r="AW15" s="83"/>
-      <c r="AX15" s="83"/>
-      <c r="AY15" s="83"/>
-      <c r="AZ15" s="83"/>
-      <c r="BA15" s="84"/>
+      <c r="AM15" s="83"/>
+      <c r="AN15" s="86"/>
+      <c r="AO15" s="86"/>
+      <c r="AP15" s="86"/>
+      <c r="AQ15" s="86"/>
+      <c r="AR15" s="86"/>
+      <c r="AS15" s="86"/>
+      <c r="AT15" s="86"/>
+      <c r="AU15" s="86"/>
+      <c r="AV15" s="86"/>
+      <c r="AW15" s="86"/>
+      <c r="AX15" s="86"/>
+      <c r="AY15" s="86"/>
+      <c r="AZ15" s="86"/>
+      <c r="BA15" s="85"/>
       <c r="BB15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="3"/>
-      <c r="C16" s="82"/>
-      <c r="Q16" s="84"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="87"/>
+      <c r="N16" s="87"/>
+      <c r="O16" s="87"/>
+      <c r="P16" s="87"/>
+      <c r="Q16" s="85"/>
       <c r="R16" s="2"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="82"/>
-      <c r="AI16" s="84"/>
+      <c r="U16" s="83"/>
+      <c r="V16" s="87"/>
+      <c r="W16" s="87"/>
+      <c r="X16" s="87"/>
+      <c r="Y16" s="87"/>
+      <c r="Z16" s="87"/>
+      <c r="AA16" s="87"/>
+      <c r="AB16" s="87"/>
+      <c r="AC16" s="87"/>
+      <c r="AD16" s="87"/>
+      <c r="AE16" s="87"/>
+      <c r="AF16" s="87"/>
+      <c r="AG16" s="87"/>
+      <c r="AH16" s="87"/>
+      <c r="AI16" s="85"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
-      <c r="AM16" s="82"/>
-      <c r="BA16" s="84"/>
+      <c r="AM16" s="83"/>
+      <c r="BA16" s="85"/>
       <c r="BB16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="3"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="84"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="88"/>
+      <c r="I17" s="88"/>
+      <c r="J17" s="88"/>
+      <c r="K17" s="88"/>
+      <c r="L17" s="88"/>
+      <c r="M17" s="88"/>
+      <c r="N17" s="88"/>
+      <c r="O17" s="88"/>
+      <c r="P17" s="88"/>
+      <c r="Q17" s="85"/>
       <c r="R17" s="2"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="82"/>
-      <c r="V17" s="83"/>
-      <c r="W17" s="83"/>
-      <c r="X17" s="83"/>
-      <c r="Y17" s="83"/>
-      <c r="Z17" s="83"/>
-      <c r="AA17" s="83"/>
-      <c r="AB17" s="83"/>
-      <c r="AC17" s="83"/>
-      <c r="AD17" s="83"/>
-      <c r="AE17" s="83"/>
-      <c r="AF17" s="83"/>
-      <c r="AG17" s="83"/>
-      <c r="AH17" s="83"/>
-      <c r="AI17" s="84"/>
+      <c r="U17" s="83"/>
+      <c r="V17" s="84"/>
+      <c r="W17" s="84"/>
+      <c r="X17" s="84"/>
+      <c r="Y17" s="84"/>
+      <c r="Z17" s="84"/>
+      <c r="AA17" s="84"/>
+      <c r="AB17" s="84"/>
+      <c r="AC17" s="84"/>
+      <c r="AD17" s="84"/>
+      <c r="AE17" s="84"/>
+      <c r="AF17" s="84"/>
+      <c r="AG17" s="84"/>
+      <c r="AH17" s="84"/>
+      <c r="AI17" s="85"/>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
-      <c r="AM17" s="82"/>
-      <c r="AN17" s="83"/>
-      <c r="AO17" s="83"/>
-      <c r="AP17" s="83"/>
-      <c r="AQ17" s="83"/>
-      <c r="AR17" s="83"/>
-      <c r="AS17" s="83"/>
-      <c r="AT17" s="83"/>
-      <c r="AU17" s="83"/>
-      <c r="AV17" s="83"/>
-      <c r="AW17" s="83"/>
-      <c r="AX17" s="83"/>
-      <c r="AY17" s="83"/>
-      <c r="AZ17" s="83"/>
-      <c r="BA17" s="84"/>
+      <c r="AM17" s="83"/>
+      <c r="AN17" s="86"/>
+      <c r="AO17" s="86"/>
+      <c r="AP17" s="86"/>
+      <c r="AQ17" s="86"/>
+      <c r="AR17" s="86"/>
+      <c r="AS17" s="86"/>
+      <c r="AT17" s="86"/>
+      <c r="AU17" s="86"/>
+      <c r="AV17" s="86"/>
+      <c r="AW17" s="86"/>
+      <c r="AX17" s="86"/>
+      <c r="AY17" s="86"/>
+      <c r="AZ17" s="86"/>
+      <c r="BA17" s="85"/>
       <c r="BB17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3"/>
       <c r="C18" s="61"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="86"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="87"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="89"/>
+      <c r="N18" s="89"/>
+      <c r="O18" s="89"/>
+      <c r="P18" s="89"/>
+      <c r="Q18" s="90"/>
       <c r="R18" s="2"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
-      <c r="U18" s="82"/>
-      <c r="AI18" s="84"/>
+      <c r="U18" s="83"/>
+      <c r="V18" s="87"/>
+      <c r="W18" s="87"/>
+      <c r="X18" s="87"/>
+      <c r="Y18" s="87"/>
+      <c r="Z18" s="87"/>
+      <c r="AA18" s="87"/>
+      <c r="AB18" s="87"/>
+      <c r="AC18" s="87"/>
+      <c r="AD18" s="87"/>
+      <c r="AE18" s="87"/>
+      <c r="AF18" s="87"/>
+      <c r="AG18" s="87"/>
+      <c r="AH18" s="87"/>
+      <c r="AI18" s="85"/>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
-      <c r="AM18" s="82"/>
-      <c r="BA18" s="84"/>
+      <c r="AM18" s="83"/>
+      <c r="BA18" s="85"/>
       <c r="BB18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8110,39 +8217,39 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="82"/>
-      <c r="V19" s="83"/>
-      <c r="W19" s="83"/>
-      <c r="X19" s="83"/>
-      <c r="Y19" s="83"/>
-      <c r="Z19" s="83"/>
-      <c r="AA19" s="83"/>
-      <c r="AB19" s="83"/>
-      <c r="AC19" s="83"/>
-      <c r="AD19" s="83"/>
-      <c r="AE19" s="83"/>
-      <c r="AF19" s="83"/>
-      <c r="AG19" s="83"/>
-      <c r="AH19" s="83"/>
-      <c r="AI19" s="84"/>
+      <c r="U19" s="83"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="85"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
-      <c r="AM19" s="82"/>
-      <c r="AN19" s="83"/>
-      <c r="AO19" s="83"/>
-      <c r="AP19" s="83"/>
-      <c r="AQ19" s="83"/>
-      <c r="AR19" s="83"/>
-      <c r="AS19" s="83"/>
-      <c r="AT19" s="83"/>
-      <c r="AU19" s="83"/>
-      <c r="AV19" s="83"/>
-      <c r="AW19" s="83"/>
-      <c r="AX19" s="83"/>
-      <c r="AY19" s="83"/>
-      <c r="AZ19" s="83"/>
-      <c r="BA19" s="84"/>
+      <c r="AM19" s="83"/>
+      <c r="AN19" s="86"/>
+      <c r="AO19" s="86"/>
+      <c r="AP19" s="86"/>
+      <c r="AQ19" s="86"/>
+      <c r="AR19" s="86"/>
+      <c r="AS19" s="86"/>
+      <c r="AT19" s="86"/>
+      <c r="AU19" s="86"/>
+      <c r="AV19" s="86"/>
+      <c r="AW19" s="86"/>
+      <c r="AX19" s="86"/>
+      <c r="AY19" s="86"/>
+      <c r="AZ19" s="86"/>
+      <c r="BA19" s="85"/>
       <c r="BB19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8167,13 +8274,26 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
-      <c r="U20" s="82"/>
-      <c r="AI20" s="84"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="87"/>
+      <c r="W20" s="87"/>
+      <c r="X20" s="87"/>
+      <c r="Y20" s="87"/>
+      <c r="Z20" s="87"/>
+      <c r="AA20" s="87"/>
+      <c r="AB20" s="87"/>
+      <c r="AC20" s="87"/>
+      <c r="AD20" s="87"/>
+      <c r="AE20" s="87"/>
+      <c r="AF20" s="87"/>
+      <c r="AG20" s="87"/>
+      <c r="AH20" s="87"/>
+      <c r="AI20" s="85"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
-      <c r="AM20" s="82"/>
-      <c r="BA20" s="84"/>
+      <c r="AM20" s="83"/>
+      <c r="BA20" s="85"/>
       <c r="BB20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8198,39 +8318,39 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="82"/>
-      <c r="V21" s="83"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="83"/>
-      <c r="Y21" s="83"/>
-      <c r="Z21" s="83"/>
-      <c r="AA21" s="83"/>
-      <c r="AB21" s="83"/>
-      <c r="AC21" s="83"/>
-      <c r="AD21" s="83"/>
-      <c r="AE21" s="83"/>
-      <c r="AF21" s="83"/>
-      <c r="AG21" s="83"/>
-      <c r="AH21" s="83"/>
-      <c r="AI21" s="84"/>
+      <c r="U21" s="83"/>
+      <c r="V21" s="84"/>
+      <c r="W21" s="84"/>
+      <c r="X21" s="84"/>
+      <c r="Y21" s="84"/>
+      <c r="Z21" s="84"/>
+      <c r="AA21" s="84"/>
+      <c r="AB21" s="84"/>
+      <c r="AC21" s="84"/>
+      <c r="AD21" s="84"/>
+      <c r="AE21" s="84"/>
+      <c r="AF21" s="84"/>
+      <c r="AG21" s="84"/>
+      <c r="AH21" s="84"/>
+      <c r="AI21" s="85"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
-      <c r="AM21" s="82"/>
-      <c r="AN21" s="83"/>
-      <c r="AO21" s="83"/>
-      <c r="AP21" s="83"/>
-      <c r="AQ21" s="83"/>
-      <c r="AR21" s="83"/>
-      <c r="AS21" s="83"/>
-      <c r="AT21" s="83"/>
-      <c r="AU21" s="83"/>
-      <c r="AV21" s="83"/>
-      <c r="AW21" s="83"/>
-      <c r="AX21" s="83"/>
-      <c r="AY21" s="83"/>
-      <c r="AZ21" s="83"/>
-      <c r="BA21" s="84"/>
+      <c r="AM21" s="83"/>
+      <c r="AN21" s="86"/>
+      <c r="AO21" s="86"/>
+      <c r="AP21" s="86"/>
+      <c r="AQ21" s="86"/>
+      <c r="AR21" s="86"/>
+      <c r="AS21" s="86"/>
+      <c r="AT21" s="86"/>
+      <c r="AU21" s="86"/>
+      <c r="AV21" s="86"/>
+      <c r="AW21" s="86"/>
+      <c r="AX21" s="86"/>
+      <c r="AY21" s="86"/>
+      <c r="AZ21" s="86"/>
+      <c r="BA21" s="85"/>
       <c r="BB21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8254,57 +8374,57 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="61"/>
-      <c r="V22" s="86"/>
-      <c r="W22" s="86"/>
-      <c r="X22" s="86"/>
-      <c r="Y22" s="86"/>
-      <c r="Z22" s="86"/>
-      <c r="AA22" s="86"/>
-      <c r="AB22" s="86"/>
-      <c r="AC22" s="86"/>
-      <c r="AD22" s="86"/>
-      <c r="AE22" s="86"/>
-      <c r="AF22" s="86"/>
-      <c r="AG22" s="86"/>
-      <c r="AH22" s="86"/>
-      <c r="AI22" s="87"/>
+      <c r="V22" s="89"/>
+      <c r="W22" s="89"/>
+      <c r="X22" s="89"/>
+      <c r="Y22" s="89"/>
+      <c r="Z22" s="89"/>
+      <c r="AA22" s="89"/>
+      <c r="AB22" s="89"/>
+      <c r="AC22" s="89"/>
+      <c r="AD22" s="89"/>
+      <c r="AE22" s="89"/>
+      <c r="AF22" s="89"/>
+      <c r="AG22" s="89"/>
+      <c r="AH22" s="89"/>
+      <c r="AI22" s="90"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
       <c r="AM22" s="61"/>
-      <c r="AN22" s="86"/>
-      <c r="AO22" s="86"/>
-      <c r="AP22" s="86"/>
-      <c r="AQ22" s="86"/>
-      <c r="AR22" s="86"/>
-      <c r="AS22" s="86"/>
-      <c r="AT22" s="86"/>
-      <c r="AU22" s="86"/>
-      <c r="AV22" s="86"/>
-      <c r="AW22" s="86"/>
-      <c r="AX22" s="86"/>
-      <c r="AY22" s="86"/>
-      <c r="AZ22" s="86"/>
-      <c r="BA22" s="87"/>
+      <c r="AN22" s="91"/>
+      <c r="AO22" s="91"/>
+      <c r="AP22" s="91"/>
+      <c r="AQ22" s="91"/>
+      <c r="AR22" s="91"/>
+      <c r="AS22" s="91"/>
+      <c r="AT22" s="91"/>
+      <c r="AU22" s="91"/>
+      <c r="AV22" s="91"/>
+      <c r="AW22" s="91"/>
+      <c r="AX22" s="91"/>
+      <c r="AY22" s="91"/>
+      <c r="AZ22" s="91"/>
+      <c r="BA22" s="90"/>
       <c r="BB22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="3"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="84"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="84"/>
+      <c r="P23" s="84"/>
+      <c r="Q23" s="85"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
@@ -8345,8 +8465,21 @@
     </row>
     <row r="24" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="3"/>
-      <c r="C24" s="82"/>
-      <c r="Q24" s="84"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="87"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="87"/>
+      <c r="M24" s="87"/>
+      <c r="N24" s="87"/>
+      <c r="O24" s="87"/>
+      <c r="P24" s="87"/>
+      <c r="Q24" s="85"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
@@ -8391,21 +8524,21 @@
     </row>
     <row r="25" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="3"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="83"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="84"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="84"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="84"/>
+      <c r="P25" s="84"/>
+      <c r="Q25" s="85"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
@@ -8450,185 +8583,224 @@
     </row>
     <row r="26" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="3"/>
-      <c r="C26" s="82"/>
-      <c r="Q26" s="84"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="87"/>
+      <c r="L26" s="87"/>
+      <c r="M26" s="87"/>
+      <c r="N26" s="87"/>
+      <c r="O26" s="87"/>
+      <c r="P26" s="87"/>
+      <c r="Q26" s="85"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="79"/>
-      <c r="V26" s="80"/>
-      <c r="W26" s="80"/>
-      <c r="X26" s="80"/>
-      <c r="Y26" s="80"/>
-      <c r="Z26" s="80"/>
-      <c r="AA26" s="80"/>
-      <c r="AB26" s="80"/>
-      <c r="AC26" s="80"/>
-      <c r="AD26" s="80"/>
-      <c r="AE26" s="80"/>
-      <c r="AF26" s="80"/>
-      <c r="AG26" s="80"/>
-      <c r="AH26" s="80"/>
+      <c r="V26" s="82"/>
+      <c r="W26" s="82"/>
+      <c r="X26" s="82"/>
+      <c r="Y26" s="82"/>
+      <c r="Z26" s="82"/>
+      <c r="AA26" s="82"/>
+      <c r="AB26" s="82"/>
+      <c r="AC26" s="82"/>
+      <c r="AD26" s="82"/>
+      <c r="AE26" s="82"/>
+      <c r="AF26" s="82"/>
+      <c r="AG26" s="82"/>
+      <c r="AH26" s="82"/>
       <c r="AI26" s="81"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
       <c r="AM26" s="79"/>
-      <c r="AN26" s="80"/>
-      <c r="AO26" s="80"/>
-      <c r="AP26" s="80"/>
-      <c r="AQ26" s="80"/>
-      <c r="AR26" s="80"/>
-      <c r="AS26" s="80"/>
-      <c r="AT26" s="80"/>
-      <c r="AU26" s="80"/>
-      <c r="AV26" s="80"/>
-      <c r="AW26" s="80"/>
-      <c r="AX26" s="80"/>
-      <c r="AY26" s="80"/>
-      <c r="AZ26" s="80"/>
+      <c r="AN26" s="82"/>
+      <c r="AO26" s="82"/>
+      <c r="AP26" s="82"/>
+      <c r="AQ26" s="82"/>
+      <c r="AR26" s="82"/>
+      <c r="AS26" s="82"/>
+      <c r="AT26" s="82"/>
+      <c r="AU26" s="82"/>
+      <c r="AV26" s="82"/>
+      <c r="AW26" s="82"/>
+      <c r="AX26" s="82"/>
+      <c r="AY26" s="82"/>
+      <c r="AZ26" s="82"/>
       <c r="BA26" s="81"/>
       <c r="BB26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="3"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="83"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="84"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="84"/>
+      <c r="P27" s="84"/>
+      <c r="Q27" s="85"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="82"/>
-      <c r="V27" s="83"/>
-      <c r="W27" s="83"/>
-      <c r="X27" s="83"/>
-      <c r="Y27" s="83"/>
-      <c r="Z27" s="83"/>
-      <c r="AA27" s="83"/>
-      <c r="AB27" s="83"/>
-      <c r="AC27" s="83"/>
-      <c r="AD27" s="83"/>
-      <c r="AE27" s="83"/>
-      <c r="AF27" s="83"/>
-      <c r="AG27" s="83"/>
-      <c r="AH27" s="83"/>
-      <c r="AI27" s="84"/>
+      <c r="U27" s="83"/>
+      <c r="V27" s="86"/>
+      <c r="W27" s="86"/>
+      <c r="X27" s="86"/>
+      <c r="Y27" s="86"/>
+      <c r="Z27" s="86"/>
+      <c r="AA27" s="86"/>
+      <c r="AB27" s="86"/>
+      <c r="AC27" s="86"/>
+      <c r="AD27" s="86"/>
+      <c r="AE27" s="86"/>
+      <c r="AF27" s="86"/>
+      <c r="AG27" s="86"/>
+      <c r="AH27" s="86"/>
+      <c r="AI27" s="85"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
-      <c r="AM27" s="82"/>
-      <c r="AN27" s="83"/>
-      <c r="AO27" s="83"/>
-      <c r="AP27" s="83"/>
-      <c r="AQ27" s="83"/>
-      <c r="AR27" s="83"/>
-      <c r="AS27" s="83"/>
-      <c r="AT27" s="83"/>
-      <c r="AU27" s="83"/>
-      <c r="AV27" s="83"/>
-      <c r="AW27" s="83"/>
-      <c r="AX27" s="83"/>
-      <c r="AY27" s="83"/>
-      <c r="AZ27" s="83"/>
-      <c r="BA27" s="84"/>
+      <c r="AM27" s="83"/>
+      <c r="AN27" s="86"/>
+      <c r="AO27" s="86"/>
+      <c r="AP27" s="86"/>
+      <c r="AQ27" s="86"/>
+      <c r="AR27" s="86"/>
+      <c r="AS27" s="86"/>
+      <c r="AT27" s="86"/>
+      <c r="AU27" s="86"/>
+      <c r="AV27" s="86"/>
+      <c r="AW27" s="86"/>
+      <c r="AX27" s="86"/>
+      <c r="AY27" s="86"/>
+      <c r="AZ27" s="86"/>
+      <c r="BA27" s="85"/>
       <c r="BB27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="3"/>
-      <c r="C28" s="82"/>
-      <c r="Q28" s="84"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="87"/>
+      <c r="K28" s="87"/>
+      <c r="L28" s="87"/>
+      <c r="M28" s="87"/>
+      <c r="N28" s="87"/>
+      <c r="O28" s="87"/>
+      <c r="P28" s="87"/>
+      <c r="Q28" s="85"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="82"/>
-      <c r="AI28" s="84"/>
+      <c r="U28" s="83"/>
+      <c r="AI28" s="85"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
-      <c r="AM28" s="82"/>
-      <c r="BA28" s="84"/>
+      <c r="AM28" s="83"/>
+      <c r="BA28" s="85"/>
       <c r="BB28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="3"/>
-      <c r="C29" s="82"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="83"/>
-      <c r="P29" s="83"/>
-      <c r="Q29" s="84"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="84"/>
+      <c r="Q29" s="85"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
-      <c r="U29" s="82"/>
-      <c r="V29" s="83"/>
-      <c r="W29" s="83"/>
-      <c r="X29" s="83"/>
-      <c r="Y29" s="83"/>
-      <c r="Z29" s="83"/>
-      <c r="AA29" s="83"/>
-      <c r="AB29" s="83"/>
-      <c r="AC29" s="83"/>
-      <c r="AD29" s="83"/>
-      <c r="AE29" s="83"/>
-      <c r="AF29" s="83"/>
-      <c r="AG29" s="83"/>
-      <c r="AH29" s="83"/>
-      <c r="AI29" s="84"/>
+      <c r="U29" s="83"/>
+      <c r="V29" s="86"/>
+      <c r="W29" s="86"/>
+      <c r="X29" s="86"/>
+      <c r="Y29" s="86"/>
+      <c r="Z29" s="86"/>
+      <c r="AA29" s="86"/>
+      <c r="AB29" s="86"/>
+      <c r="AC29" s="86"/>
+      <c r="AD29" s="86"/>
+      <c r="AE29" s="86"/>
+      <c r="AF29" s="86"/>
+      <c r="AG29" s="86"/>
+      <c r="AH29" s="86"/>
+      <c r="AI29" s="85"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
-      <c r="AM29" s="82"/>
-      <c r="AN29" s="83"/>
-      <c r="AO29" s="83"/>
-      <c r="AP29" s="83"/>
-      <c r="AQ29" s="83"/>
-      <c r="AR29" s="83"/>
-      <c r="AS29" s="83"/>
-      <c r="AT29" s="83"/>
-      <c r="AU29" s="83"/>
-      <c r="AV29" s="83"/>
-      <c r="AW29" s="83"/>
-      <c r="AX29" s="83"/>
-      <c r="AY29" s="83"/>
-      <c r="AZ29" s="83"/>
-      <c r="BA29" s="84"/>
+      <c r="AM29" s="83"/>
+      <c r="AN29" s="86"/>
+      <c r="AO29" s="86"/>
+      <c r="AP29" s="86"/>
+      <c r="AQ29" s="86"/>
+      <c r="AR29" s="86"/>
+      <c r="AS29" s="86"/>
+      <c r="AT29" s="86"/>
+      <c r="AU29" s="86"/>
+      <c r="AV29" s="86"/>
+      <c r="AW29" s="86"/>
+      <c r="AX29" s="86"/>
+      <c r="AY29" s="86"/>
+      <c r="AZ29" s="86"/>
+      <c r="BA29" s="85"/>
       <c r="BB29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="3"/>
-      <c r="C30" s="82"/>
-      <c r="Q30" s="84"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="87"/>
+      <c r="K30" s="87"/>
+      <c r="L30" s="87"/>
+      <c r="M30" s="87"/>
+      <c r="N30" s="87"/>
+      <c r="O30" s="87"/>
+      <c r="P30" s="87"/>
+      <c r="Q30" s="85"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="82"/>
-      <c r="AI30" s="84"/>
+      <c r="U30" s="83"/>
+      <c r="AI30" s="85"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
-      <c r="AM30" s="82"/>
+      <c r="AM30" s="83"/>
       <c r="AN30" s="9"/>
       <c r="AO30" s="9"/>
       <c r="AP30" s="9"/>
@@ -8642,133 +8814,146 @@
       <c r="AX30" s="9"/>
       <c r="AY30" s="9"/>
       <c r="AZ30" s="9"/>
-      <c r="BA30" s="84"/>
+      <c r="BA30" s="85"/>
       <c r="BB30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="3"/>
-      <c r="C31" s="82"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="83"/>
-      <c r="P31" s="83"/>
-      <c r="Q31" s="84"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="84"/>
+      <c r="O31" s="84"/>
+      <c r="P31" s="84"/>
+      <c r="Q31" s="85"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="82"/>
-      <c r="V31" s="83"/>
-      <c r="W31" s="83"/>
-      <c r="X31" s="83"/>
-      <c r="Y31" s="83"/>
-      <c r="Z31" s="83"/>
-      <c r="AA31" s="83"/>
-      <c r="AB31" s="83"/>
-      <c r="AC31" s="83"/>
-      <c r="AD31" s="83"/>
-      <c r="AE31" s="83"/>
-      <c r="AF31" s="83"/>
-      <c r="AG31" s="83"/>
-      <c r="AH31" s="83"/>
-      <c r="AI31" s="84"/>
+      <c r="U31" s="83"/>
+      <c r="V31" s="86"/>
+      <c r="W31" s="86"/>
+      <c r="X31" s="86"/>
+      <c r="Y31" s="86"/>
+      <c r="Z31" s="86"/>
+      <c r="AA31" s="86"/>
+      <c r="AB31" s="86"/>
+      <c r="AC31" s="86"/>
+      <c r="AD31" s="86"/>
+      <c r="AE31" s="86"/>
+      <c r="AF31" s="86"/>
+      <c r="AG31" s="86"/>
+      <c r="AH31" s="86"/>
+      <c r="AI31" s="85"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
-      <c r="AM31" s="82"/>
-      <c r="AN31" s="83"/>
-      <c r="AO31" s="83"/>
-      <c r="AP31" s="83"/>
-      <c r="AQ31" s="83"/>
-      <c r="AR31" s="83"/>
-      <c r="AS31" s="83"/>
-      <c r="AT31" s="83"/>
-      <c r="AU31" s="83"/>
-      <c r="AV31" s="83"/>
-      <c r="AW31" s="83"/>
-      <c r="AX31" s="83"/>
-      <c r="AY31" s="83"/>
-      <c r="AZ31" s="83"/>
-      <c r="BA31" s="84"/>
+      <c r="AM31" s="83"/>
+      <c r="AN31" s="86"/>
+      <c r="AO31" s="86"/>
+      <c r="AP31" s="86"/>
+      <c r="AQ31" s="86"/>
+      <c r="AR31" s="86"/>
+      <c r="AS31" s="86"/>
+      <c r="AT31" s="86"/>
+      <c r="AU31" s="86"/>
+      <c r="AV31" s="86"/>
+      <c r="AW31" s="86"/>
+      <c r="AX31" s="86"/>
+      <c r="AY31" s="86"/>
+      <c r="AZ31" s="86"/>
+      <c r="BA31" s="85"/>
       <c r="BB31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="3"/>
-      <c r="C32" s="82"/>
-      <c r="Q32" s="84"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="87"/>
+      <c r="K32" s="87"/>
+      <c r="L32" s="87"/>
+      <c r="M32" s="87"/>
+      <c r="N32" s="87"/>
+      <c r="O32" s="87"/>
+      <c r="P32" s="87"/>
+      <c r="Q32" s="85"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="82"/>
-      <c r="AI32" s="84"/>
+      <c r="U32" s="83"/>
+      <c r="AI32" s="85"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
-      <c r="AM32" s="82"/>
-      <c r="BA32" s="84"/>
+      <c r="AM32" s="83"/>
+      <c r="BA32" s="85"/>
       <c r="BB32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="3"/>
       <c r="C33" s="61"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="86"/>
-      <c r="H33" s="86"/>
-      <c r="I33" s="86"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="86"/>
-      <c r="M33" s="86"/>
-      <c r="N33" s="86"/>
-      <c r="O33" s="86"/>
-      <c r="P33" s="86"/>
-      <c r="Q33" s="87"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="89"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="89"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="89"/>
+      <c r="M33" s="89"/>
+      <c r="N33" s="89"/>
+      <c r="O33" s="89"/>
+      <c r="P33" s="89"/>
+      <c r="Q33" s="90"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="82"/>
-      <c r="V33" s="83"/>
-      <c r="W33" s="83"/>
-      <c r="X33" s="83"/>
-      <c r="Y33" s="83"/>
-      <c r="Z33" s="83"/>
-      <c r="AA33" s="83"/>
-      <c r="AB33" s="83"/>
-      <c r="AC33" s="83"/>
-      <c r="AD33" s="83"/>
-      <c r="AE33" s="83"/>
-      <c r="AF33" s="83"/>
-      <c r="AG33" s="83"/>
-      <c r="AH33" s="83"/>
-      <c r="AI33" s="84"/>
+      <c r="U33" s="83"/>
+      <c r="V33" s="86"/>
+      <c r="W33" s="86"/>
+      <c r="X33" s="86"/>
+      <c r="Y33" s="86"/>
+      <c r="Z33" s="86"/>
+      <c r="AA33" s="86"/>
+      <c r="AB33" s="86"/>
+      <c r="AC33" s="86"/>
+      <c r="AD33" s="86"/>
+      <c r="AE33" s="86"/>
+      <c r="AF33" s="86"/>
+      <c r="AG33" s="86"/>
+      <c r="AH33" s="86"/>
+      <c r="AI33" s="85"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
-      <c r="AM33" s="82"/>
-      <c r="AN33" s="83"/>
-      <c r="AO33" s="83"/>
-      <c r="AP33" s="83"/>
-      <c r="AQ33" s="83"/>
-      <c r="AR33" s="83"/>
-      <c r="AS33" s="83"/>
-      <c r="AT33" s="83"/>
-      <c r="AU33" s="83"/>
-      <c r="AV33" s="83"/>
-      <c r="AW33" s="83"/>
-      <c r="AX33" s="83"/>
-      <c r="AY33" s="83"/>
-      <c r="AZ33" s="83"/>
-      <c r="BA33" s="84"/>
+      <c r="AM33" s="83"/>
+      <c r="AN33" s="86"/>
+      <c r="AO33" s="86"/>
+      <c r="AP33" s="86"/>
+      <c r="AQ33" s="86"/>
+      <c r="AR33" s="86"/>
+      <c r="AS33" s="86"/>
+      <c r="AT33" s="86"/>
+      <c r="AU33" s="86"/>
+      <c r="AV33" s="86"/>
+      <c r="AW33" s="86"/>
+      <c r="AX33" s="86"/>
+      <c r="AY33" s="86"/>
+      <c r="AZ33" s="86"/>
+      <c r="BA33" s="85"/>
       <c r="BB33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8791,13 +8976,13 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="82"/>
-      <c r="AI34" s="84"/>
+      <c r="U34" s="83"/>
+      <c r="AI34" s="85"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
-      <c r="AM34" s="82"/>
-      <c r="BA34" s="84"/>
+      <c r="AM34" s="83"/>
+      <c r="BA34" s="85"/>
       <c r="BB34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8822,39 +9007,39 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
-      <c r="U35" s="82"/>
-      <c r="V35" s="83"/>
-      <c r="W35" s="83"/>
-      <c r="X35" s="83"/>
-      <c r="Y35" s="83"/>
-      <c r="Z35" s="83"/>
-      <c r="AA35" s="83"/>
-      <c r="AB35" s="83"/>
-      <c r="AC35" s="83"/>
-      <c r="AD35" s="83"/>
-      <c r="AE35" s="83"/>
-      <c r="AF35" s="83"/>
-      <c r="AG35" s="83"/>
-      <c r="AH35" s="83"/>
-      <c r="AI35" s="84"/>
+      <c r="U35" s="83"/>
+      <c r="V35" s="86"/>
+      <c r="W35" s="86"/>
+      <c r="X35" s="86"/>
+      <c r="Y35" s="86"/>
+      <c r="Z35" s="86"/>
+      <c r="AA35" s="86"/>
+      <c r="AB35" s="86"/>
+      <c r="AC35" s="86"/>
+      <c r="AD35" s="86"/>
+      <c r="AE35" s="86"/>
+      <c r="AF35" s="86"/>
+      <c r="AG35" s="86"/>
+      <c r="AH35" s="86"/>
+      <c r="AI35" s="85"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
-      <c r="AM35" s="82"/>
-      <c r="AN35" s="83"/>
-      <c r="AO35" s="83"/>
-      <c r="AP35" s="83"/>
-      <c r="AQ35" s="83"/>
-      <c r="AR35" s="83"/>
-      <c r="AS35" s="83"/>
-      <c r="AT35" s="83"/>
-      <c r="AU35" s="83"/>
-      <c r="AV35" s="83"/>
-      <c r="AW35" s="83"/>
-      <c r="AX35" s="83"/>
-      <c r="AY35" s="83"/>
-      <c r="AZ35" s="83"/>
-      <c r="BA35" s="84"/>
+      <c r="AM35" s="83"/>
+      <c r="AN35" s="86"/>
+      <c r="AO35" s="86"/>
+      <c r="AP35" s="86"/>
+      <c r="AQ35" s="86"/>
+      <c r="AR35" s="86"/>
+      <c r="AS35" s="86"/>
+      <c r="AT35" s="86"/>
+      <c r="AU35" s="86"/>
+      <c r="AV35" s="86"/>
+      <c r="AW35" s="86"/>
+      <c r="AX35" s="86"/>
+      <c r="AY35" s="86"/>
+      <c r="AZ35" s="86"/>
+      <c r="BA35" s="85"/>
       <c r="BB35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8879,26 +9064,26 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
-      <c r="U36" s="82"/>
-      <c r="AI36" s="84"/>
+      <c r="U36" s="83"/>
+      <c r="AI36" s="85"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
       <c r="AM36" s="61"/>
-      <c r="AN36" s="86"/>
-      <c r="AO36" s="86"/>
-      <c r="AP36" s="86"/>
-      <c r="AQ36" s="86"/>
-      <c r="AR36" s="86"/>
-      <c r="AS36" s="86"/>
-      <c r="AT36" s="86"/>
-      <c r="AU36" s="86"/>
-      <c r="AV36" s="86"/>
-      <c r="AW36" s="86"/>
-      <c r="AX36" s="86"/>
-      <c r="AY36" s="86"/>
-      <c r="AZ36" s="86"/>
-      <c r="BA36" s="87"/>
+      <c r="AN36" s="91"/>
+      <c r="AO36" s="91"/>
+      <c r="AP36" s="91"/>
+      <c r="AQ36" s="91"/>
+      <c r="AR36" s="91"/>
+      <c r="AS36" s="91"/>
+      <c r="AT36" s="91"/>
+      <c r="AU36" s="91"/>
+      <c r="AV36" s="91"/>
+      <c r="AW36" s="91"/>
+      <c r="AX36" s="91"/>
+      <c r="AY36" s="91"/>
+      <c r="AZ36" s="91"/>
+      <c r="BA36" s="90"/>
       <c r="BB36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8921,21 +9106,21 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
-      <c r="U37" s="82"/>
-      <c r="V37" s="83"/>
-      <c r="W37" s="83"/>
-      <c r="X37" s="83"/>
-      <c r="Y37" s="83"/>
-      <c r="Z37" s="83"/>
-      <c r="AA37" s="83"/>
-      <c r="AB37" s="83"/>
-      <c r="AC37" s="83"/>
-      <c r="AD37" s="83"/>
-      <c r="AE37" s="83"/>
-      <c r="AF37" s="83"/>
-      <c r="AG37" s="83"/>
-      <c r="AH37" s="83"/>
-      <c r="AI37" s="84"/>
+      <c r="U37" s="83"/>
+      <c r="V37" s="86"/>
+      <c r="W37" s="86"/>
+      <c r="X37" s="86"/>
+      <c r="Y37" s="86"/>
+      <c r="Z37" s="86"/>
+      <c r="AA37" s="86"/>
+      <c r="AB37" s="86"/>
+      <c r="AC37" s="86"/>
+      <c r="AD37" s="86"/>
+      <c r="AE37" s="86"/>
+      <c r="AF37" s="86"/>
+      <c r="AG37" s="86"/>
+      <c r="AH37" s="86"/>
+      <c r="AI37" s="85"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
@@ -8958,39 +9143,39 @@
     </row>
     <row r="38" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="3"/>
-      <c r="C38" s="82"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
-      <c r="O38" s="83"/>
-      <c r="P38" s="83"/>
-      <c r="Q38" s="84"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="84"/>
+      <c r="I38" s="84"/>
+      <c r="J38" s="84"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="84"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="84"/>
+      <c r="O38" s="84"/>
+      <c r="P38" s="84"/>
+      <c r="Q38" s="85"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="61"/>
-      <c r="V38" s="86"/>
-      <c r="W38" s="86"/>
-      <c r="X38" s="86"/>
-      <c r="Y38" s="86"/>
-      <c r="Z38" s="86"/>
-      <c r="AA38" s="86"/>
-      <c r="AB38" s="86"/>
-      <c r="AC38" s="86"/>
-      <c r="AD38" s="86"/>
-      <c r="AE38" s="86"/>
-      <c r="AF38" s="86"/>
-      <c r="AG38" s="86"/>
-      <c r="AH38" s="86"/>
-      <c r="AI38" s="87"/>
+      <c r="V38" s="91"/>
+      <c r="W38" s="91"/>
+      <c r="X38" s="91"/>
+      <c r="Y38" s="91"/>
+      <c r="Z38" s="91"/>
+      <c r="AA38" s="91"/>
+      <c r="AB38" s="91"/>
+      <c r="AC38" s="91"/>
+      <c r="AD38" s="91"/>
+      <c r="AE38" s="91"/>
+      <c r="AF38" s="91"/>
+      <c r="AG38" s="91"/>
+      <c r="AH38" s="91"/>
+      <c r="AI38" s="90"/>
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
@@ -9015,8 +9200,21 @@
     </row>
     <row r="39" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="3"/>
-      <c r="C39" s="82"/>
-      <c r="Q39" s="84"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="87"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="87"/>
+      <c r="G39" s="87"/>
+      <c r="H39" s="87"/>
+      <c r="I39" s="87"/>
+      <c r="J39" s="87"/>
+      <c r="K39" s="87"/>
+      <c r="L39" s="87"/>
+      <c r="M39" s="87"/>
+      <c r="N39" s="87"/>
+      <c r="O39" s="87"/>
+      <c r="P39" s="87"/>
+      <c r="Q39" s="85"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
@@ -9059,21 +9257,21 @@
     </row>
     <row r="40" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="3"/>
-      <c r="C40" s="82"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="83"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="83"/>
-      <c r="O40" s="83"/>
-      <c r="P40" s="83"/>
-      <c r="Q40" s="84"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="84"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="84"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="84"/>
+      <c r="O40" s="84"/>
+      <c r="P40" s="84"/>
+      <c r="Q40" s="85"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
@@ -9098,26 +9296,39 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="79"/>
-      <c r="AN40" s="80"/>
-      <c r="AO40" s="80"/>
-      <c r="AP40" s="80"/>
-      <c r="AQ40" s="80"/>
-      <c r="AR40" s="80"/>
-      <c r="AS40" s="80"/>
-      <c r="AT40" s="80"/>
-      <c r="AU40" s="80"/>
-      <c r="AV40" s="80"/>
-      <c r="AW40" s="80"/>
-      <c r="AX40" s="80"/>
-      <c r="AY40" s="80"/>
-      <c r="AZ40" s="80"/>
+      <c r="AN40" s="82"/>
+      <c r="AO40" s="82"/>
+      <c r="AP40" s="82"/>
+      <c r="AQ40" s="82"/>
+      <c r="AR40" s="82"/>
+      <c r="AS40" s="82"/>
+      <c r="AT40" s="82"/>
+      <c r="AU40" s="82"/>
+      <c r="AV40" s="82"/>
+      <c r="AW40" s="82"/>
+      <c r="AX40" s="82"/>
+      <c r="AY40" s="82"/>
+      <c r="AZ40" s="82"/>
       <c r="BA40" s="81"/>
       <c r="BB40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="3"/>
-      <c r="C41" s="82"/>
-      <c r="Q41" s="84"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="87"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="87"/>
+      <c r="H41" s="87"/>
+      <c r="I41" s="87"/>
+      <c r="J41" s="87"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="87"/>
+      <c r="M41" s="87"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="87"/>
+      <c r="P41" s="87"/>
+      <c r="Q41" s="85"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -9141,133 +9352,146 @@
       <c r="AJ41" s="3"/>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
-      <c r="AM41" s="82"/>
-      <c r="AN41" s="83"/>
-      <c r="AO41" s="83"/>
-      <c r="AP41" s="83"/>
-      <c r="AQ41" s="83"/>
-      <c r="AR41" s="83"/>
-      <c r="AS41" s="83"/>
-      <c r="AT41" s="83"/>
-      <c r="AU41" s="83"/>
-      <c r="AV41" s="83"/>
-      <c r="AW41" s="83"/>
-      <c r="AX41" s="83"/>
-      <c r="AY41" s="83"/>
-      <c r="AZ41" s="83"/>
-      <c r="BA41" s="84"/>
+      <c r="AM41" s="83"/>
+      <c r="AN41" s="86"/>
+      <c r="AO41" s="86"/>
+      <c r="AP41" s="86"/>
+      <c r="AQ41" s="86"/>
+      <c r="AR41" s="86"/>
+      <c r="AS41" s="86"/>
+      <c r="AT41" s="86"/>
+      <c r="AU41" s="86"/>
+      <c r="AV41" s="86"/>
+      <c r="AW41" s="86"/>
+      <c r="AX41" s="86"/>
+      <c r="AY41" s="86"/>
+      <c r="AZ41" s="86"/>
+      <c r="BA41" s="85"/>
       <c r="BB41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="3"/>
-      <c r="C42" s="82"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="83"/>
-      <c r="M42" s="83"/>
-      <c r="N42" s="83"/>
-      <c r="O42" s="83"/>
-      <c r="P42" s="83"/>
-      <c r="Q42" s="84"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="84"/>
+      <c r="I42" s="84"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="84"/>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+      <c r="N42" s="84"/>
+      <c r="O42" s="84"/>
+      <c r="P42" s="84"/>
+      <c r="Q42" s="85"/>
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="79"/>
-      <c r="V42" s="80"/>
-      <c r="W42" s="80"/>
-      <c r="X42" s="80"/>
-      <c r="Y42" s="80"/>
-      <c r="Z42" s="80"/>
-      <c r="AA42" s="80"/>
-      <c r="AB42" s="80"/>
-      <c r="AC42" s="80"/>
-      <c r="AD42" s="80"/>
-      <c r="AE42" s="80"/>
-      <c r="AF42" s="80"/>
-      <c r="AG42" s="80"/>
-      <c r="AH42" s="80"/>
+      <c r="V42" s="82"/>
+      <c r="W42" s="82"/>
+      <c r="X42" s="82"/>
+      <c r="Y42" s="82"/>
+      <c r="Z42" s="82"/>
+      <c r="AA42" s="82"/>
+      <c r="AB42" s="82"/>
+      <c r="AC42" s="82"/>
+      <c r="AD42" s="82"/>
+      <c r="AE42" s="82"/>
+      <c r="AF42" s="82"/>
+      <c r="AG42" s="82"/>
+      <c r="AH42" s="82"/>
       <c r="AI42" s="81"/>
       <c r="AJ42" s="3"/>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
-      <c r="AM42" s="82"/>
-      <c r="BA42" s="84"/>
+      <c r="AM42" s="83"/>
+      <c r="BA42" s="85"/>
       <c r="BB42" s="3"/>
     </row>
     <row r="43" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="3"/>
-      <c r="C43" s="82"/>
-      <c r="Q43" s="84"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="87"/>
+      <c r="E43" s="87"/>
+      <c r="F43" s="87"/>
+      <c r="G43" s="87"/>
+      <c r="H43" s="87"/>
+      <c r="I43" s="87"/>
+      <c r="J43" s="87"/>
+      <c r="K43" s="87"/>
+      <c r="L43" s="87"/>
+      <c r="M43" s="87"/>
+      <c r="N43" s="87"/>
+      <c r="O43" s="87"/>
+      <c r="P43" s="87"/>
+      <c r="Q43" s="85"/>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
-      <c r="U43" s="82"/>
-      <c r="V43" s="83"/>
-      <c r="W43" s="83"/>
-      <c r="X43" s="83"/>
-      <c r="Y43" s="83"/>
-      <c r="Z43" s="83"/>
-      <c r="AA43" s="83"/>
-      <c r="AB43" s="83"/>
-      <c r="AC43" s="83"/>
-      <c r="AD43" s="83"/>
-      <c r="AE43" s="83"/>
-      <c r="AF43" s="83"/>
-      <c r="AG43" s="83"/>
-      <c r="AH43" s="83"/>
-      <c r="AI43" s="84"/>
+      <c r="U43" s="83"/>
+      <c r="V43" s="86"/>
+      <c r="W43" s="86"/>
+      <c r="X43" s="86"/>
+      <c r="Y43" s="86"/>
+      <c r="Z43" s="86"/>
+      <c r="AA43" s="86"/>
+      <c r="AB43" s="86"/>
+      <c r="AC43" s="86"/>
+      <c r="AD43" s="86"/>
+      <c r="AE43" s="86"/>
+      <c r="AF43" s="86"/>
+      <c r="AG43" s="86"/>
+      <c r="AH43" s="86"/>
+      <c r="AI43" s="85"/>
       <c r="AJ43" s="3"/>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
-      <c r="AM43" s="82"/>
-      <c r="AN43" s="83"/>
-      <c r="AO43" s="83"/>
-      <c r="AP43" s="83"/>
-      <c r="AQ43" s="83"/>
-      <c r="AR43" s="83"/>
-      <c r="AS43" s="83"/>
-      <c r="AT43" s="83"/>
-      <c r="AU43" s="83"/>
-      <c r="AV43" s="83"/>
-      <c r="AW43" s="83"/>
-      <c r="AX43" s="83"/>
-      <c r="AY43" s="83"/>
-      <c r="AZ43" s="83"/>
-      <c r="BA43" s="84"/>
+      <c r="AM43" s="83"/>
+      <c r="AN43" s="86"/>
+      <c r="AO43" s="86"/>
+      <c r="AP43" s="86"/>
+      <c r="AQ43" s="86"/>
+      <c r="AR43" s="86"/>
+      <c r="AS43" s="86"/>
+      <c r="AT43" s="86"/>
+      <c r="AU43" s="86"/>
+      <c r="AV43" s="86"/>
+      <c r="AW43" s="86"/>
+      <c r="AX43" s="86"/>
+      <c r="AY43" s="86"/>
+      <c r="AZ43" s="86"/>
+      <c r="BA43" s="85"/>
       <c r="BB43" s="3"/>
     </row>
     <row r="44" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="3"/>
-      <c r="C44" s="82"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="83"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="83"/>
-      <c r="O44" s="83"/>
-      <c r="P44" s="83"/>
-      <c r="Q44" s="84"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="84"/>
+      <c r="E44" s="84"/>
+      <c r="F44" s="84"/>
+      <c r="G44" s="84"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="84"/>
+      <c r="J44" s="84"/>
+      <c r="K44" s="84"/>
+      <c r="L44" s="84"/>
+      <c r="M44" s="84"/>
+      <c r="N44" s="84"/>
+      <c r="O44" s="84"/>
+      <c r="P44" s="84"/>
+      <c r="Q44" s="85"/>
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
-      <c r="U44" s="82"/>
-      <c r="AI44" s="84"/>
+      <c r="U44" s="83"/>
+      <c r="AI44" s="85"/>
       <c r="AJ44" s="3"/>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
-      <c r="AM44" s="82"/>
+      <c r="AM44" s="83"/>
       <c r="AN44" s="9"/>
       <c r="AO44" s="9"/>
       <c r="AP44" s="9"/>
@@ -9281,73 +9505,86 @@
       <c r="AX44" s="9"/>
       <c r="AY44" s="9"/>
       <c r="AZ44" s="9"/>
-      <c r="BA44" s="84"/>
+      <c r="BA44" s="85"/>
       <c r="BB44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="3"/>
-      <c r="C45" s="82"/>
-      <c r="Q45" s="84"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="87"/>
+      <c r="E45" s="87"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="87"/>
+      <c r="H45" s="87"/>
+      <c r="I45" s="87"/>
+      <c r="J45" s="87"/>
+      <c r="K45" s="87"/>
+      <c r="L45" s="87"/>
+      <c r="M45" s="87"/>
+      <c r="N45" s="87"/>
+      <c r="O45" s="87"/>
+      <c r="P45" s="87"/>
+      <c r="Q45" s="85"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
-      <c r="U45" s="82"/>
-      <c r="V45" s="83"/>
-      <c r="W45" s="83"/>
-      <c r="X45" s="83"/>
-      <c r="Y45" s="83"/>
-      <c r="Z45" s="83"/>
-      <c r="AA45" s="83"/>
-      <c r="AB45" s="83"/>
-      <c r="AC45" s="83"/>
-      <c r="AD45" s="83"/>
-      <c r="AE45" s="83"/>
-      <c r="AF45" s="83"/>
-      <c r="AG45" s="83"/>
-      <c r="AH45" s="83"/>
-      <c r="AI45" s="84"/>
+      <c r="U45" s="83"/>
+      <c r="V45" s="86"/>
+      <c r="W45" s="86"/>
+      <c r="X45" s="86"/>
+      <c r="Y45" s="86"/>
+      <c r="Z45" s="86"/>
+      <c r="AA45" s="86"/>
+      <c r="AB45" s="86"/>
+      <c r="AC45" s="86"/>
+      <c r="AD45" s="86"/>
+      <c r="AE45" s="86"/>
+      <c r="AF45" s="86"/>
+      <c r="AG45" s="86"/>
+      <c r="AH45" s="86"/>
+      <c r="AI45" s="85"/>
       <c r="AJ45" s="3"/>
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
       <c r="AM45" s="61"/>
-      <c r="AN45" s="86"/>
-      <c r="AO45" s="86"/>
-      <c r="AP45" s="86"/>
-      <c r="AQ45" s="86"/>
-      <c r="AR45" s="86"/>
-      <c r="AS45" s="86"/>
-      <c r="AT45" s="86"/>
-      <c r="AU45" s="86"/>
-      <c r="AV45" s="86"/>
-      <c r="AW45" s="86"/>
-      <c r="AX45" s="86"/>
-      <c r="AY45" s="86"/>
-      <c r="AZ45" s="86"/>
-      <c r="BA45" s="87"/>
+      <c r="AN45" s="91"/>
+      <c r="AO45" s="91"/>
+      <c r="AP45" s="91"/>
+      <c r="AQ45" s="91"/>
+      <c r="AR45" s="91"/>
+      <c r="AS45" s="91"/>
+      <c r="AT45" s="91"/>
+      <c r="AU45" s="91"/>
+      <c r="AV45" s="91"/>
+      <c r="AW45" s="91"/>
+      <c r="AX45" s="91"/>
+      <c r="AY45" s="91"/>
+      <c r="AZ45" s="91"/>
+      <c r="BA45" s="90"/>
       <c r="BB45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="3"/>
-      <c r="C46" s="82"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="83"/>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="83"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
-      <c r="L46" s="83"/>
-      <c r="M46" s="83"/>
-      <c r="N46" s="83"/>
-      <c r="O46" s="83"/>
-      <c r="P46" s="83"/>
-      <c r="Q46" s="84"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="84"/>
+      <c r="E46" s="84"/>
+      <c r="F46" s="84"/>
+      <c r="G46" s="84"/>
+      <c r="H46" s="84"/>
+      <c r="I46" s="84"/>
+      <c r="J46" s="84"/>
+      <c r="K46" s="84"/>
+      <c r="L46" s="84"/>
+      <c r="M46" s="84"/>
+      <c r="N46" s="84"/>
+      <c r="O46" s="84"/>
+      <c r="P46" s="84"/>
+      <c r="Q46" s="85"/>
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
-      <c r="U46" s="82"/>
-      <c r="AI46" s="84"/>
+      <c r="U46" s="83"/>
+      <c r="AI46" s="85"/>
       <c r="AJ46" s="3"/>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
@@ -9370,26 +9607,39 @@
     </row>
     <row r="47" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="3"/>
-      <c r="C47" s="82"/>
-      <c r="Q47" s="84"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="87"/>
+      <c r="E47" s="87"/>
+      <c r="F47" s="87"/>
+      <c r="G47" s="87"/>
+      <c r="H47" s="87"/>
+      <c r="I47" s="87"/>
+      <c r="J47" s="87"/>
+      <c r="K47" s="87"/>
+      <c r="L47" s="87"/>
+      <c r="M47" s="87"/>
+      <c r="N47" s="87"/>
+      <c r="O47" s="87"/>
+      <c r="P47" s="87"/>
+      <c r="Q47" s="85"/>
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
-      <c r="U47" s="82"/>
-      <c r="V47" s="83"/>
-      <c r="W47" s="83"/>
-      <c r="X47" s="83"/>
-      <c r="Y47" s="83"/>
-      <c r="Z47" s="83"/>
-      <c r="AA47" s="83"/>
-      <c r="AB47" s="83"/>
-      <c r="AC47" s="83"/>
-      <c r="AD47" s="83"/>
-      <c r="AE47" s="83"/>
-      <c r="AF47" s="83"/>
-      <c r="AG47" s="83"/>
-      <c r="AH47" s="83"/>
-      <c r="AI47" s="84"/>
+      <c r="U47" s="83"/>
+      <c r="V47" s="86"/>
+      <c r="W47" s="86"/>
+      <c r="X47" s="86"/>
+      <c r="Y47" s="86"/>
+      <c r="Z47" s="86"/>
+      <c r="AA47" s="86"/>
+      <c r="AB47" s="86"/>
+      <c r="AC47" s="86"/>
+      <c r="AD47" s="86"/>
+      <c r="AE47" s="86"/>
+      <c r="AF47" s="86"/>
+      <c r="AG47" s="86"/>
+      <c r="AH47" s="86"/>
+      <c r="AI47" s="85"/>
       <c r="AJ47" s="3"/>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
@@ -9414,26 +9664,26 @@
     </row>
     <row r="48" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="3"/>
-      <c r="C48" s="82"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-      <c r="L48" s="83"/>
-      <c r="M48" s="83"/>
-      <c r="N48" s="83"/>
-      <c r="O48" s="83"/>
-      <c r="P48" s="83"/>
-      <c r="Q48" s="84"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="84"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="84"/>
+      <c r="I48" s="84"/>
+      <c r="J48" s="84"/>
+      <c r="K48" s="84"/>
+      <c r="L48" s="84"/>
+      <c r="M48" s="84"/>
+      <c r="N48" s="84"/>
+      <c r="O48" s="84"/>
+      <c r="P48" s="84"/>
+      <c r="Q48" s="85"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
-      <c r="U48" s="82"/>
-      <c r="AI48" s="84"/>
+      <c r="U48" s="83"/>
+      <c r="AI48" s="85"/>
       <c r="AJ48" s="3"/>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
@@ -9458,199 +9708,225 @@
     </row>
     <row r="49" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="3"/>
-      <c r="C49" s="82"/>
-      <c r="Q49" s="84"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="87"/>
+      <c r="E49" s="87"/>
+      <c r="F49" s="87"/>
+      <c r="G49" s="87"/>
+      <c r="H49" s="87"/>
+      <c r="I49" s="87"/>
+      <c r="J49" s="87"/>
+      <c r="K49" s="87"/>
+      <c r="L49" s="87"/>
+      <c r="M49" s="87"/>
+      <c r="N49" s="87"/>
+      <c r="O49" s="87"/>
+      <c r="P49" s="87"/>
+      <c r="Q49" s="85"/>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
-      <c r="U49" s="82"/>
-      <c r="V49" s="83"/>
-      <c r="W49" s="83"/>
-      <c r="X49" s="83"/>
-      <c r="Y49" s="83"/>
-      <c r="Z49" s="83"/>
-      <c r="AA49" s="83"/>
-      <c r="AB49" s="83"/>
-      <c r="AC49" s="83"/>
-      <c r="AD49" s="83"/>
-      <c r="AE49" s="83"/>
-      <c r="AF49" s="83"/>
-      <c r="AG49" s="83"/>
-      <c r="AH49" s="83"/>
-      <c r="AI49" s="84"/>
+      <c r="U49" s="83"/>
+      <c r="V49" s="86"/>
+      <c r="W49" s="86"/>
+      <c r="X49" s="86"/>
+      <c r="Y49" s="86"/>
+      <c r="Z49" s="86"/>
+      <c r="AA49" s="86"/>
+      <c r="AB49" s="86"/>
+      <c r="AC49" s="86"/>
+      <c r="AD49" s="86"/>
+      <c r="AE49" s="86"/>
+      <c r="AF49" s="86"/>
+      <c r="AG49" s="86"/>
+      <c r="AH49" s="86"/>
+      <c r="AI49" s="85"/>
       <c r="AJ49" s="3"/>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
       <c r="AM49" s="79"/>
-      <c r="AN49" s="80"/>
-      <c r="AO49" s="80"/>
-      <c r="AP49" s="80"/>
-      <c r="AQ49" s="80"/>
-      <c r="AR49" s="80"/>
-      <c r="AS49" s="80"/>
-      <c r="AT49" s="80"/>
-      <c r="AU49" s="80"/>
-      <c r="AV49" s="80"/>
-      <c r="AW49" s="80"/>
-      <c r="AX49" s="80"/>
-      <c r="AY49" s="80"/>
-      <c r="AZ49" s="80"/>
+      <c r="AN49" s="82"/>
+      <c r="AO49" s="82"/>
+      <c r="AP49" s="82"/>
+      <c r="AQ49" s="82"/>
+      <c r="AR49" s="82"/>
+      <c r="AS49" s="82"/>
+      <c r="AT49" s="82"/>
+      <c r="AU49" s="82"/>
+      <c r="AV49" s="82"/>
+      <c r="AW49" s="82"/>
+      <c r="AX49" s="82"/>
+      <c r="AY49" s="82"/>
+      <c r="AZ49" s="82"/>
       <c r="BA49" s="81"/>
       <c r="BB49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="3"/>
-      <c r="C50" s="82"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="83"/>
-      <c r="L50" s="83"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="83"/>
-      <c r="O50" s="83"/>
-      <c r="P50" s="83"/>
-      <c r="Q50" s="84"/>
+      <c r="C50" s="83"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="84"/>
+      <c r="J50" s="84"/>
+      <c r="K50" s="84"/>
+      <c r="L50" s="84"/>
+      <c r="M50" s="84"/>
+      <c r="N50" s="84"/>
+      <c r="O50" s="84"/>
+      <c r="P50" s="84"/>
+      <c r="Q50" s="85"/>
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
-      <c r="U50" s="82"/>
-      <c r="AI50" s="84"/>
+      <c r="U50" s="83"/>
+      <c r="AI50" s="85"/>
       <c r="AJ50" s="3"/>
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
-      <c r="AM50" s="82"/>
-      <c r="AN50" s="83"/>
-      <c r="AO50" s="83"/>
-      <c r="AP50" s="83"/>
-      <c r="AQ50" s="83"/>
-      <c r="AR50" s="83"/>
-      <c r="AS50" s="83"/>
-      <c r="AT50" s="83"/>
-      <c r="AU50" s="83"/>
-      <c r="AV50" s="83"/>
-      <c r="AW50" s="83"/>
-      <c r="AX50" s="83"/>
-      <c r="AY50" s="83"/>
-      <c r="AZ50" s="83"/>
-      <c r="BA50" s="84"/>
+      <c r="AM50" s="83"/>
+      <c r="AN50" s="86"/>
+      <c r="AO50" s="86"/>
+      <c r="AP50" s="86"/>
+      <c r="AQ50" s="86"/>
+      <c r="AR50" s="86"/>
+      <c r="AS50" s="86"/>
+      <c r="AT50" s="86"/>
+      <c r="AU50" s="86"/>
+      <c r="AV50" s="86"/>
+      <c r="AW50" s="86"/>
+      <c r="AX50" s="86"/>
+      <c r="AY50" s="86"/>
+      <c r="AZ50" s="86"/>
+      <c r="BA50" s="85"/>
       <c r="BB50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="3"/>
-      <c r="C51" s="82"/>
-      <c r="Q51" s="84"/>
+      <c r="C51" s="83"/>
+      <c r="D51" s="87"/>
+      <c r="E51" s="87"/>
+      <c r="F51" s="87"/>
+      <c r="G51" s="87"/>
+      <c r="H51" s="87"/>
+      <c r="I51" s="87"/>
+      <c r="J51" s="87"/>
+      <c r="K51" s="87"/>
+      <c r="L51" s="87"/>
+      <c r="M51" s="87"/>
+      <c r="N51" s="87"/>
+      <c r="O51" s="87"/>
+      <c r="P51" s="87"/>
+      <c r="Q51" s="85"/>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
-      <c r="U51" s="82"/>
-      <c r="V51" s="83"/>
-      <c r="W51" s="83"/>
-      <c r="X51" s="83"/>
-      <c r="Y51" s="83"/>
-      <c r="Z51" s="83"/>
-      <c r="AA51" s="83"/>
-      <c r="AB51" s="83"/>
-      <c r="AC51" s="83"/>
-      <c r="AD51" s="83"/>
-      <c r="AE51" s="83"/>
-      <c r="AF51" s="83"/>
-      <c r="AG51" s="83"/>
-      <c r="AH51" s="83"/>
-      <c r="AI51" s="84"/>
+      <c r="U51" s="83"/>
+      <c r="V51" s="86"/>
+      <c r="W51" s="86"/>
+      <c r="X51" s="86"/>
+      <c r="Y51" s="86"/>
+      <c r="Z51" s="86"/>
+      <c r="AA51" s="86"/>
+      <c r="AB51" s="86"/>
+      <c r="AC51" s="86"/>
+      <c r="AD51" s="86"/>
+      <c r="AE51" s="86"/>
+      <c r="AF51" s="86"/>
+      <c r="AG51" s="86"/>
+      <c r="AH51" s="86"/>
+      <c r="AI51" s="85"/>
       <c r="AJ51" s="3"/>
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
-      <c r="AM51" s="82"/>
-      <c r="BA51" s="84"/>
+      <c r="AM51" s="83"/>
+      <c r="BA51" s="85"/>
       <c r="BB51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="3"/>
-      <c r="C52" s="82"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="83"/>
-      <c r="O52" s="83"/>
-      <c r="P52" s="83"/>
-      <c r="Q52" s="84"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="84"/>
+      <c r="E52" s="84"/>
+      <c r="F52" s="84"/>
+      <c r="G52" s="84"/>
+      <c r="H52" s="84"/>
+      <c r="I52" s="84"/>
+      <c r="J52" s="84"/>
+      <c r="K52" s="84"/>
+      <c r="L52" s="84"/>
+      <c r="M52" s="84"/>
+      <c r="N52" s="84"/>
+      <c r="O52" s="84"/>
+      <c r="P52" s="84"/>
+      <c r="Q52" s="85"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
-      <c r="U52" s="82"/>
-      <c r="AI52" s="84"/>
+      <c r="U52" s="83"/>
+      <c r="AI52" s="85"/>
       <c r="AJ52" s="3"/>
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
-      <c r="AM52" s="82"/>
-      <c r="AN52" s="83"/>
-      <c r="AO52" s="83"/>
-      <c r="AP52" s="83"/>
-      <c r="AQ52" s="83"/>
-      <c r="AR52" s="83"/>
-      <c r="AS52" s="83"/>
-      <c r="AT52" s="83"/>
-      <c r="AU52" s="83"/>
-      <c r="AV52" s="83"/>
-      <c r="AW52" s="83"/>
-      <c r="AX52" s="83"/>
-      <c r="AY52" s="83"/>
-      <c r="AZ52" s="83"/>
-      <c r="BA52" s="84"/>
+      <c r="AM52" s="83"/>
+      <c r="AN52" s="86"/>
+      <c r="AO52" s="86"/>
+      <c r="AP52" s="86"/>
+      <c r="AQ52" s="86"/>
+      <c r="AR52" s="86"/>
+      <c r="AS52" s="86"/>
+      <c r="AT52" s="86"/>
+      <c r="AU52" s="86"/>
+      <c r="AV52" s="86"/>
+      <c r="AW52" s="86"/>
+      <c r="AX52" s="86"/>
+      <c r="AY52" s="86"/>
+      <c r="AZ52" s="86"/>
+      <c r="BA52" s="85"/>
       <c r="BB52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="3"/>
       <c r="C53" s="61"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="86"/>
-      <c r="H53" s="86"/>
-      <c r="I53" s="86"/>
-      <c r="J53" s="86"/>
-      <c r="K53" s="86"/>
-      <c r="L53" s="86"/>
-      <c r="M53" s="86"/>
-      <c r="N53" s="86"/>
-      <c r="O53" s="86"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="87"/>
+      <c r="D53" s="89"/>
+      <c r="E53" s="89"/>
+      <c r="F53" s="89"/>
+      <c r="G53" s="89"/>
+      <c r="H53" s="89"/>
+      <c r="I53" s="89"/>
+      <c r="J53" s="89"/>
+      <c r="K53" s="89"/>
+      <c r="L53" s="89"/>
+      <c r="M53" s="89"/>
+      <c r="N53" s="89"/>
+      <c r="O53" s="89"/>
+      <c r="P53" s="89"/>
+      <c r="Q53" s="90"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
-      <c r="U53" s="82"/>
-      <c r="AI53" s="84"/>
-      <c r="AJ53" s="88"/>
+      <c r="U53" s="83"/>
+      <c r="AI53" s="85"/>
+      <c r="AJ53" s="92"/>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
       <c r="AM53" s="61"/>
-      <c r="AN53" s="86"/>
-      <c r="AO53" s="86"/>
-      <c r="AP53" s="86"/>
-      <c r="AQ53" s="86"/>
-      <c r="AR53" s="86"/>
-      <c r="AS53" s="86"/>
-      <c r="AT53" s="86"/>
-      <c r="AU53" s="86"/>
-      <c r="AV53" s="86"/>
-      <c r="AW53" s="86"/>
-      <c r="AX53" s="86"/>
-      <c r="AY53" s="86"/>
-      <c r="AZ53" s="86"/>
-      <c r="BA53" s="87"/>
+      <c r="AN53" s="91"/>
+      <c r="AO53" s="91"/>
+      <c r="AP53" s="91"/>
+      <c r="AQ53" s="91"/>
+      <c r="AR53" s="91"/>
+      <c r="AS53" s="91"/>
+      <c r="AT53" s="91"/>
+      <c r="AU53" s="91"/>
+      <c r="AV53" s="91"/>
+      <c r="AW53" s="91"/>
+      <c r="AX53" s="91"/>
+      <c r="AY53" s="91"/>
+      <c r="AZ53" s="91"/>
+      <c r="BA53" s="90"/>
       <c r="BB53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9673,21 +9949,21 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="2"/>
-      <c r="U54" s="89"/>
-      <c r="V54" s="89"/>
-      <c r="W54" s="89"/>
-      <c r="X54" s="89"/>
-      <c r="Y54" s="89"/>
-      <c r="Z54" s="89"/>
-      <c r="AA54" s="89"/>
-      <c r="AB54" s="89"/>
-      <c r="AC54" s="89"/>
-      <c r="AD54" s="89"/>
-      <c r="AE54" s="89"/>
-      <c r="AF54" s="89"/>
-      <c r="AG54" s="89"/>
-      <c r="AH54" s="89"/>
-      <c r="AI54" s="89"/>
+      <c r="U54" s="93"/>
+      <c r="V54" s="93"/>
+      <c r="W54" s="93"/>
+      <c r="X54" s="93"/>
+      <c r="Y54" s="93"/>
+      <c r="Z54" s="93"/>
+      <c r="AA54" s="93"/>
+      <c r="AB54" s="93"/>
+      <c r="AC54" s="93"/>
+      <c r="AD54" s="93"/>
+      <c r="AE54" s="93"/>
+      <c r="AF54" s="93"/>
+      <c r="AG54" s="93"/>
+      <c r="AH54" s="93"/>
+      <c r="AI54" s="93"/>
       <c r="AJ54" s="2"/>
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
@@ -9709,7 +9985,7 @@
       <c r="BB54" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="139">
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="P3:AA3"/>
     <mergeCell ref="AC3:AN3"/>
@@ -9724,24 +10000,135 @@
     <mergeCell ref="C9:Q9"/>
     <mergeCell ref="U9:AI9"/>
     <mergeCell ref="AM9:BA9"/>
+    <mergeCell ref="D10:P10"/>
+    <mergeCell ref="V10:AH10"/>
+    <mergeCell ref="AN10:AZ10"/>
+    <mergeCell ref="D11:P11"/>
+    <mergeCell ref="V11:AH11"/>
+    <mergeCell ref="AN11:AZ11"/>
+    <mergeCell ref="D12:P12"/>
+    <mergeCell ref="V12:AH12"/>
+    <mergeCell ref="AN12:AZ12"/>
+    <mergeCell ref="D13:P13"/>
+    <mergeCell ref="V13:AH13"/>
+    <mergeCell ref="AN13:AZ13"/>
+    <mergeCell ref="D14:P14"/>
+    <mergeCell ref="V14:AH14"/>
+    <mergeCell ref="AN14:AZ14"/>
+    <mergeCell ref="D15:P15"/>
+    <mergeCell ref="V15:AH15"/>
+    <mergeCell ref="AN15:AZ15"/>
+    <mergeCell ref="D16:P16"/>
+    <mergeCell ref="V16:AH16"/>
+    <mergeCell ref="AN16:AZ16"/>
+    <mergeCell ref="D17:P17"/>
+    <mergeCell ref="V17:AH17"/>
+    <mergeCell ref="AN17:AZ17"/>
+    <mergeCell ref="D18:P18"/>
+    <mergeCell ref="V18:AH18"/>
+    <mergeCell ref="AN18:AZ18"/>
+    <mergeCell ref="V19:AH19"/>
+    <mergeCell ref="AN19:AZ19"/>
     <mergeCell ref="C20:Q20"/>
+    <mergeCell ref="V20:AH20"/>
+    <mergeCell ref="AN20:AZ20"/>
     <mergeCell ref="C21:Q21"/>
+    <mergeCell ref="V21:AH21"/>
+    <mergeCell ref="AN21:AZ21"/>
+    <mergeCell ref="D22:P22"/>
+    <mergeCell ref="V22:AH22"/>
+    <mergeCell ref="AN22:AZ22"/>
+    <mergeCell ref="D23:P23"/>
+    <mergeCell ref="D24:P24"/>
     <mergeCell ref="U24:AI24"/>
     <mergeCell ref="AM24:BA24"/>
+    <mergeCell ref="D25:P25"/>
     <mergeCell ref="U25:AI25"/>
     <mergeCell ref="AM25:BA25"/>
+    <mergeCell ref="D26:P26"/>
+    <mergeCell ref="V26:AH26"/>
+    <mergeCell ref="AN26:AZ26"/>
+    <mergeCell ref="D27:P27"/>
+    <mergeCell ref="V27:AH27"/>
+    <mergeCell ref="AN27:AZ27"/>
+    <mergeCell ref="D28:P28"/>
+    <mergeCell ref="V28:AH28"/>
+    <mergeCell ref="AN28:AZ28"/>
+    <mergeCell ref="D29:P29"/>
+    <mergeCell ref="V29:AH29"/>
+    <mergeCell ref="AN29:AZ29"/>
+    <mergeCell ref="D30:P30"/>
+    <mergeCell ref="V30:AH30"/>
+    <mergeCell ref="AN30:AZ30"/>
+    <mergeCell ref="D31:P31"/>
+    <mergeCell ref="V31:AH31"/>
+    <mergeCell ref="AN31:AZ31"/>
+    <mergeCell ref="D32:P32"/>
+    <mergeCell ref="V32:AH32"/>
+    <mergeCell ref="AN32:AZ32"/>
+    <mergeCell ref="D33:P33"/>
+    <mergeCell ref="V33:AH33"/>
+    <mergeCell ref="AN33:AZ33"/>
+    <mergeCell ref="V34:AH34"/>
+    <mergeCell ref="AN34:AZ34"/>
     <mergeCell ref="C35:Q35"/>
+    <mergeCell ref="V35:AH35"/>
+    <mergeCell ref="AN35:AZ35"/>
     <mergeCell ref="C36:Q36"/>
+    <mergeCell ref="V36:AH36"/>
+    <mergeCell ref="AN36:AZ36"/>
+    <mergeCell ref="D37:P37"/>
+    <mergeCell ref="V37:AH37"/>
+    <mergeCell ref="D38:P38"/>
+    <mergeCell ref="V38:AH38"/>
     <mergeCell ref="AM38:BA38"/>
+    <mergeCell ref="D39:P39"/>
     <mergeCell ref="AM39:BA39"/>
+    <mergeCell ref="D40:P40"/>
     <mergeCell ref="U40:AI40"/>
+    <mergeCell ref="AN40:AZ40"/>
+    <mergeCell ref="D41:P41"/>
     <mergeCell ref="U41:AI41"/>
+    <mergeCell ref="AN41:AZ41"/>
+    <mergeCell ref="D42:P42"/>
+    <mergeCell ref="V42:AH42"/>
+    <mergeCell ref="AN42:AZ42"/>
+    <mergeCell ref="D43:P43"/>
+    <mergeCell ref="V43:AH43"/>
+    <mergeCell ref="AN43:AZ43"/>
+    <mergeCell ref="D44:P44"/>
+    <mergeCell ref="V44:AH44"/>
+    <mergeCell ref="AN44:AZ44"/>
+    <mergeCell ref="D45:P45"/>
+    <mergeCell ref="V45:AH45"/>
+    <mergeCell ref="AN45:AZ45"/>
+    <mergeCell ref="D46:P46"/>
+    <mergeCell ref="V46:AH46"/>
+    <mergeCell ref="D47:P47"/>
+    <mergeCell ref="V47:AH47"/>
     <mergeCell ref="AM47:BA47"/>
+    <mergeCell ref="D48:P48"/>
+    <mergeCell ref="V48:AH48"/>
     <mergeCell ref="AM48:BA48"/>
+    <mergeCell ref="D49:P49"/>
+    <mergeCell ref="V49:AH49"/>
+    <mergeCell ref="AN49:AZ49"/>
+    <mergeCell ref="D50:P50"/>
+    <mergeCell ref="V50:AH50"/>
+    <mergeCell ref="AN50:AZ50"/>
+    <mergeCell ref="D51:P51"/>
+    <mergeCell ref="V51:AH51"/>
+    <mergeCell ref="AN51:AZ51"/>
+    <mergeCell ref="D52:P52"/>
+    <mergeCell ref="V52:AH52"/>
+    <mergeCell ref="AN52:AZ52"/>
+    <mergeCell ref="D53:P53"/>
+    <mergeCell ref="V53:AH53"/>
+    <mergeCell ref="AN53:AZ53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/xardas/main/templates/doc/chx-blank.xlsx
+++ b/xardas/main/templates/doc/chx-blank.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Страница 1" sheetId="1" state="visible" r:id="rId2"/>
@@ -569,7 +569,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -906,7 +906,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -914,15 +914,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1019,7 +1015,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -4334,8 +4330,8 @@
     <mergeCell ref="P50:S53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4344,7 +4340,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -7328,8 +7324,8 @@
     <mergeCell ref="U48:BA53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7338,7 +7334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -7468,18 +7464,18 @@
     </row>
     <row r="4" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
       <c r="O4" s="5"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
@@ -7903,6 +7899,19 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="83"/>
+      <c r="AN12" s="9"/>
+      <c r="AO12" s="9"/>
+      <c r="AP12" s="9"/>
+      <c r="AQ12" s="9"/>
+      <c r="AR12" s="9"/>
+      <c r="AS12" s="9"/>
+      <c r="AT12" s="9"/>
+      <c r="AU12" s="9"/>
+      <c r="AV12" s="9"/>
+      <c r="AW12" s="9"/>
+      <c r="AX12" s="9"/>
+      <c r="AY12" s="9"/>
+      <c r="AZ12" s="9"/>
       <c r="BA12" s="85"/>
       <c r="BB12" s="3"/>
     </row>
@@ -8000,6 +8009,19 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="83"/>
+      <c r="AN14" s="9"/>
+      <c r="AO14" s="9"/>
+      <c r="AP14" s="9"/>
+      <c r="AQ14" s="9"/>
+      <c r="AR14" s="9"/>
+      <c r="AS14" s="9"/>
+      <c r="AT14" s="9"/>
+      <c r="AU14" s="9"/>
+      <c r="AV14" s="9"/>
+      <c r="AW14" s="9"/>
+      <c r="AX14" s="9"/>
+      <c r="AY14" s="9"/>
+      <c r="AZ14" s="9"/>
       <c r="BA14" s="85"/>
       <c r="BB14" s="3"/>
     </row>
@@ -8097,25 +8119,38 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="83"/>
+      <c r="AN16" s="9"/>
+      <c r="AO16" s="9"/>
+      <c r="AP16" s="9"/>
+      <c r="AQ16" s="9"/>
+      <c r="AR16" s="9"/>
+      <c r="AS16" s="9"/>
+      <c r="AT16" s="9"/>
+      <c r="AU16" s="9"/>
+      <c r="AV16" s="9"/>
+      <c r="AW16" s="9"/>
+      <c r="AX16" s="9"/>
+      <c r="AY16" s="9"/>
+      <c r="AZ16" s="9"/>
       <c r="BA16" s="85"/>
       <c r="BB16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="3"/>
       <c r="C17" s="83"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="88"/>
-      <c r="I17" s="88"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="88"/>
-      <c r="L17" s="88"/>
-      <c r="M17" s="88"/>
-      <c r="N17" s="88"/>
-      <c r="O17" s="88"/>
-      <c r="P17" s="88"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="84"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="84"/>
+      <c r="P17" s="84"/>
       <c r="Q17" s="85"/>
       <c r="R17" s="2"/>
       <c r="S17" s="3"/>
@@ -8158,20 +8193,20 @@
     <row r="18" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3"/>
       <c r="C18" s="61"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="89"/>
-      <c r="M18" s="89"/>
-      <c r="N18" s="89"/>
-      <c r="O18" s="89"/>
-      <c r="P18" s="89"/>
-      <c r="Q18" s="90"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="88"/>
+      <c r="J18" s="88"/>
+      <c r="K18" s="88"/>
+      <c r="L18" s="88"/>
+      <c r="M18" s="88"/>
+      <c r="N18" s="88"/>
+      <c r="O18" s="88"/>
+      <c r="P18" s="88"/>
+      <c r="Q18" s="89"/>
       <c r="R18" s="2"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
@@ -8194,6 +8229,19 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="83"/>
+      <c r="AN18" s="9"/>
+      <c r="AO18" s="9"/>
+      <c r="AP18" s="9"/>
+      <c r="AQ18" s="9"/>
+      <c r="AR18" s="9"/>
+      <c r="AS18" s="9"/>
+      <c r="AT18" s="9"/>
+      <c r="AU18" s="9"/>
+      <c r="AV18" s="9"/>
+      <c r="AW18" s="9"/>
+      <c r="AX18" s="9"/>
+      <c r="AY18" s="9"/>
+      <c r="AZ18" s="9"/>
       <c r="BA18" s="85"/>
       <c r="BB18" s="3"/>
     </row>
@@ -8293,6 +8341,19 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
       <c r="AM20" s="83"/>
+      <c r="AN20" s="9"/>
+      <c r="AO20" s="9"/>
+      <c r="AP20" s="9"/>
+      <c r="AQ20" s="9"/>
+      <c r="AR20" s="9"/>
+      <c r="AS20" s="9"/>
+      <c r="AT20" s="9"/>
+      <c r="AU20" s="9"/>
+      <c r="AV20" s="9"/>
+      <c r="AW20" s="9"/>
+      <c r="AX20" s="9"/>
+      <c r="AY20" s="9"/>
+      <c r="AZ20" s="9"/>
       <c r="BA20" s="85"/>
       <c r="BB20" s="3"/>
     </row>
@@ -8374,38 +8435,38 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="61"/>
-      <c r="V22" s="89"/>
-      <c r="W22" s="89"/>
-      <c r="X22" s="89"/>
-      <c r="Y22" s="89"/>
-      <c r="Z22" s="89"/>
-      <c r="AA22" s="89"/>
-      <c r="AB22" s="89"/>
-      <c r="AC22" s="89"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="89"/>
-      <c r="AF22" s="89"/>
-      <c r="AG22" s="89"/>
-      <c r="AH22" s="89"/>
-      <c r="AI22" s="90"/>
+      <c r="V22" s="88"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="88"/>
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="88"/>
+      <c r="AD22" s="88"/>
+      <c r="AE22" s="88"/>
+      <c r="AF22" s="88"/>
+      <c r="AG22" s="88"/>
+      <c r="AH22" s="88"/>
+      <c r="AI22" s="89"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
       <c r="AM22" s="61"/>
-      <c r="AN22" s="91"/>
-      <c r="AO22" s="91"/>
-      <c r="AP22" s="91"/>
-      <c r="AQ22" s="91"/>
-      <c r="AR22" s="91"/>
-      <c r="AS22" s="91"/>
-      <c r="AT22" s="91"/>
-      <c r="AU22" s="91"/>
-      <c r="AV22" s="91"/>
-      <c r="AW22" s="91"/>
-      <c r="AX22" s="91"/>
-      <c r="AY22" s="91"/>
-      <c r="AZ22" s="91"/>
-      <c r="BA22" s="90"/>
+      <c r="AN22" s="90"/>
+      <c r="AO22" s="90"/>
+      <c r="AP22" s="90"/>
+      <c r="AQ22" s="90"/>
+      <c r="AR22" s="90"/>
+      <c r="AS22" s="90"/>
+      <c r="AT22" s="90"/>
+      <c r="AU22" s="90"/>
+      <c r="AV22" s="90"/>
+      <c r="AW22" s="90"/>
+      <c r="AX22" s="90"/>
+      <c r="AY22" s="90"/>
+      <c r="AZ22" s="90"/>
+      <c r="BA22" s="89"/>
       <c r="BB22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8712,11 +8773,37 @@
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="83"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+      <c r="AF28" s="9"/>
+      <c r="AG28" s="9"/>
+      <c r="AH28" s="9"/>
       <c r="AI28" s="85"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
       <c r="AM28" s="83"/>
+      <c r="AN28" s="9"/>
+      <c r="AO28" s="9"/>
+      <c r="AP28" s="9"/>
+      <c r="AQ28" s="9"/>
+      <c r="AR28" s="9"/>
+      <c r="AS28" s="9"/>
+      <c r="AT28" s="9"/>
+      <c r="AU28" s="9"/>
+      <c r="AV28" s="9"/>
+      <c r="AW28" s="9"/>
+      <c r="AX28" s="9"/>
+      <c r="AY28" s="9"/>
+      <c r="AZ28" s="9"/>
       <c r="BA28" s="85"/>
       <c r="BB28" s="3"/>
     </row>
@@ -8796,6 +8883,19 @@
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="83"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+      <c r="AA30" s="9"/>
+      <c r="AB30" s="9"/>
+      <c r="AC30" s="9"/>
+      <c r="AD30" s="9"/>
+      <c r="AE30" s="9"/>
+      <c r="AF30" s="9"/>
+      <c r="AG30" s="9"/>
+      <c r="AH30" s="9"/>
       <c r="AI30" s="85"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -8893,31 +8993,57 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="83"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="9"/>
+      <c r="AC32" s="9"/>
+      <c r="AD32" s="9"/>
+      <c r="AE32" s="9"/>
+      <c r="AF32" s="9"/>
+      <c r="AG32" s="9"/>
+      <c r="AH32" s="9"/>
       <c r="AI32" s="85"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
       <c r="AM32" s="83"/>
+      <c r="AN32" s="9"/>
+      <c r="AO32" s="9"/>
+      <c r="AP32" s="9"/>
+      <c r="AQ32" s="9"/>
+      <c r="AR32" s="9"/>
+      <c r="AS32" s="9"/>
+      <c r="AT32" s="9"/>
+      <c r="AU32" s="9"/>
+      <c r="AV32" s="9"/>
+      <c r="AW32" s="9"/>
+      <c r="AX32" s="9"/>
+      <c r="AY32" s="9"/>
+      <c r="AZ32" s="9"/>
       <c r="BA32" s="85"/>
       <c r="BB32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="3"/>
       <c r="C33" s="61"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="89"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="89"/>
-      <c r="K33" s="89"/>
-      <c r="L33" s="89"/>
-      <c r="M33" s="89"/>
-      <c r="N33" s="89"/>
-      <c r="O33" s="89"/>
-      <c r="P33" s="89"/>
-      <c r="Q33" s="90"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="88"/>
+      <c r="I33" s="88"/>
+      <c r="J33" s="88"/>
+      <c r="K33" s="88"/>
+      <c r="L33" s="88"/>
+      <c r="M33" s="88"/>
+      <c r="N33" s="88"/>
+      <c r="O33" s="88"/>
+      <c r="P33" s="88"/>
+      <c r="Q33" s="89"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
@@ -8977,11 +9103,37 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="83"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="9"/>
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="9"/>
+      <c r="AC34" s="9"/>
+      <c r="AD34" s="9"/>
+      <c r="AE34" s="9"/>
+      <c r="AF34" s="9"/>
+      <c r="AG34" s="9"/>
+      <c r="AH34" s="9"/>
       <c r="AI34" s="85"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
       <c r="AM34" s="83"/>
+      <c r="AN34" s="9"/>
+      <c r="AO34" s="9"/>
+      <c r="AP34" s="9"/>
+      <c r="AQ34" s="9"/>
+      <c r="AR34" s="9"/>
+      <c r="AS34" s="9"/>
+      <c r="AT34" s="9"/>
+      <c r="AU34" s="9"/>
+      <c r="AV34" s="9"/>
+      <c r="AW34" s="9"/>
+      <c r="AX34" s="9"/>
+      <c r="AY34" s="9"/>
+      <c r="AZ34" s="9"/>
       <c r="BA34" s="85"/>
       <c r="BB34" s="3"/>
     </row>
@@ -9065,25 +9217,38 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="83"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
+      <c r="AD36" s="9"/>
+      <c r="AE36" s="9"/>
+      <c r="AF36" s="9"/>
+      <c r="AG36" s="9"/>
+      <c r="AH36" s="9"/>
       <c r="AI36" s="85"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
       <c r="AM36" s="61"/>
-      <c r="AN36" s="91"/>
-      <c r="AO36" s="91"/>
-      <c r="AP36" s="91"/>
-      <c r="AQ36" s="91"/>
-      <c r="AR36" s="91"/>
-      <c r="AS36" s="91"/>
-      <c r="AT36" s="91"/>
-      <c r="AU36" s="91"/>
-      <c r="AV36" s="91"/>
-      <c r="AW36" s="91"/>
-      <c r="AX36" s="91"/>
-      <c r="AY36" s="91"/>
-      <c r="AZ36" s="91"/>
-      <c r="BA36" s="90"/>
+      <c r="AN36" s="90"/>
+      <c r="AO36" s="90"/>
+      <c r="AP36" s="90"/>
+      <c r="AQ36" s="90"/>
+      <c r="AR36" s="90"/>
+      <c r="AS36" s="90"/>
+      <c r="AT36" s="90"/>
+      <c r="AU36" s="90"/>
+      <c r="AV36" s="90"/>
+      <c r="AW36" s="90"/>
+      <c r="AX36" s="90"/>
+      <c r="AY36" s="90"/>
+      <c r="AZ36" s="90"/>
+      <c r="BA36" s="89"/>
       <c r="BB36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9162,20 +9327,20 @@
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="61"/>
-      <c r="V38" s="91"/>
-      <c r="W38" s="91"/>
-      <c r="X38" s="91"/>
-      <c r="Y38" s="91"/>
-      <c r="Z38" s="91"/>
-      <c r="AA38" s="91"/>
-      <c r="AB38" s="91"/>
-      <c r="AC38" s="91"/>
-      <c r="AD38" s="91"/>
-      <c r="AE38" s="91"/>
-      <c r="AF38" s="91"/>
-      <c r="AG38" s="91"/>
-      <c r="AH38" s="91"/>
-      <c r="AI38" s="90"/>
+      <c r="V38" s="90"/>
+      <c r="W38" s="90"/>
+      <c r="X38" s="90"/>
+      <c r="Y38" s="90"/>
+      <c r="Z38" s="90"/>
+      <c r="AA38" s="90"/>
+      <c r="AB38" s="90"/>
+      <c r="AC38" s="90"/>
+      <c r="AD38" s="90"/>
+      <c r="AE38" s="90"/>
+      <c r="AF38" s="90"/>
+      <c r="AG38" s="90"/>
+      <c r="AH38" s="90"/>
+      <c r="AI38" s="89"/>
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
@@ -9408,6 +9573,19 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
       <c r="AM42" s="83"/>
+      <c r="AN42" s="9"/>
+      <c r="AO42" s="9"/>
+      <c r="AP42" s="9"/>
+      <c r="AQ42" s="9"/>
+      <c r="AR42" s="9"/>
+      <c r="AS42" s="9"/>
+      <c r="AT42" s="9"/>
+      <c r="AU42" s="9"/>
+      <c r="AV42" s="9"/>
+      <c r="AW42" s="9"/>
+      <c r="AX42" s="9"/>
+      <c r="AY42" s="9"/>
+      <c r="AZ42" s="9"/>
       <c r="BA42" s="85"/>
       <c r="BB42" s="3"/>
     </row>
@@ -9487,6 +9665,19 @@
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="83"/>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9"/>
+      <c r="Y44" s="9"/>
+      <c r="Z44" s="9"/>
+      <c r="AA44" s="9"/>
+      <c r="AB44" s="9"/>
+      <c r="AC44" s="9"/>
+      <c r="AD44" s="9"/>
+      <c r="AE44" s="9"/>
+      <c r="AF44" s="9"/>
+      <c r="AG44" s="9"/>
+      <c r="AH44" s="9"/>
       <c r="AI44" s="85"/>
       <c r="AJ44" s="3"/>
       <c r="AK44" s="3"/>
@@ -9547,20 +9738,20 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
       <c r="AM45" s="61"/>
-      <c r="AN45" s="91"/>
-      <c r="AO45" s="91"/>
-      <c r="AP45" s="91"/>
-      <c r="AQ45" s="91"/>
-      <c r="AR45" s="91"/>
-      <c r="AS45" s="91"/>
-      <c r="AT45" s="91"/>
-      <c r="AU45" s="91"/>
-      <c r="AV45" s="91"/>
-      <c r="AW45" s="91"/>
-      <c r="AX45" s="91"/>
-      <c r="AY45" s="91"/>
-      <c r="AZ45" s="91"/>
-      <c r="BA45" s="90"/>
+      <c r="AN45" s="90"/>
+      <c r="AO45" s="90"/>
+      <c r="AP45" s="90"/>
+      <c r="AQ45" s="90"/>
+      <c r="AR45" s="90"/>
+      <c r="AS45" s="90"/>
+      <c r="AT45" s="90"/>
+      <c r="AU45" s="90"/>
+      <c r="AV45" s="90"/>
+      <c r="AW45" s="90"/>
+      <c r="AX45" s="90"/>
+      <c r="AY45" s="90"/>
+      <c r="AZ45" s="90"/>
+      <c r="BA45" s="89"/>
       <c r="BB45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9584,6 +9775,19 @@
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="83"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="9"/>
+      <c r="Y46" s="9"/>
+      <c r="Z46" s="9"/>
+      <c r="AA46" s="9"/>
+      <c r="AB46" s="9"/>
+      <c r="AC46" s="9"/>
+      <c r="AD46" s="9"/>
+      <c r="AE46" s="9"/>
+      <c r="AF46" s="9"/>
+      <c r="AG46" s="9"/>
+      <c r="AH46" s="9"/>
       <c r="AI46" s="85"/>
       <c r="AJ46" s="3"/>
       <c r="AK46" s="3"/>
@@ -9683,6 +9887,19 @@
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="83"/>
+      <c r="V48" s="9"/>
+      <c r="W48" s="9"/>
+      <c r="X48" s="9"/>
+      <c r="Y48" s="9"/>
+      <c r="Z48" s="9"/>
+      <c r="AA48" s="9"/>
+      <c r="AB48" s="9"/>
+      <c r="AC48" s="9"/>
+      <c r="AD48" s="9"/>
+      <c r="AE48" s="9"/>
+      <c r="AF48" s="9"/>
+      <c r="AG48" s="9"/>
+      <c r="AH48" s="9"/>
       <c r="AI48" s="85"/>
       <c r="AJ48" s="3"/>
       <c r="AK48" s="3"/>
@@ -9782,6 +9999,19 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="83"/>
+      <c r="V50" s="9"/>
+      <c r="W50" s="9"/>
+      <c r="X50" s="9"/>
+      <c r="Y50" s="9"/>
+      <c r="Z50" s="9"/>
+      <c r="AA50" s="9"/>
+      <c r="AB50" s="9"/>
+      <c r="AC50" s="9"/>
+      <c r="AD50" s="9"/>
+      <c r="AE50" s="9"/>
+      <c r="AF50" s="9"/>
+      <c r="AG50" s="9"/>
+      <c r="AH50" s="9"/>
       <c r="AI50" s="85"/>
       <c r="AJ50" s="3"/>
       <c r="AK50" s="3"/>
@@ -9842,6 +10072,19 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
       <c r="AM51" s="83"/>
+      <c r="AN51" s="9"/>
+      <c r="AO51" s="9"/>
+      <c r="AP51" s="9"/>
+      <c r="AQ51" s="9"/>
+      <c r="AR51" s="9"/>
+      <c r="AS51" s="9"/>
+      <c r="AT51" s="9"/>
+      <c r="AU51" s="9"/>
+      <c r="AV51" s="9"/>
+      <c r="AW51" s="9"/>
+      <c r="AX51" s="9"/>
+      <c r="AY51" s="9"/>
+      <c r="AZ51" s="9"/>
       <c r="BA51" s="85"/>
       <c r="BB51" s="3"/>
     </row>
@@ -9866,6 +10109,19 @@
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
       <c r="U52" s="83"/>
+      <c r="V52" s="9"/>
+      <c r="W52" s="9"/>
+      <c r="X52" s="9"/>
+      <c r="Y52" s="9"/>
+      <c r="Z52" s="9"/>
+      <c r="AA52" s="9"/>
+      <c r="AB52" s="9"/>
+      <c r="AC52" s="9"/>
+      <c r="AD52" s="9"/>
+      <c r="AE52" s="9"/>
+      <c r="AF52" s="9"/>
+      <c r="AG52" s="9"/>
+      <c r="AH52" s="9"/>
       <c r="AI52" s="85"/>
       <c r="AJ52" s="3"/>
       <c r="AK52" s="3"/>
@@ -9890,43 +10146,56 @@
     <row r="53" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="3"/>
       <c r="C53" s="61"/>
-      <c r="D53" s="89"/>
-      <c r="E53" s="89"/>
-      <c r="F53" s="89"/>
-      <c r="G53" s="89"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="89"/>
-      <c r="J53" s="89"/>
-      <c r="K53" s="89"/>
-      <c r="L53" s="89"/>
-      <c r="M53" s="89"/>
-      <c r="N53" s="89"/>
-      <c r="O53" s="89"/>
-      <c r="P53" s="89"/>
-      <c r="Q53" s="90"/>
+      <c r="D53" s="88"/>
+      <c r="E53" s="88"/>
+      <c r="F53" s="88"/>
+      <c r="G53" s="88"/>
+      <c r="H53" s="88"/>
+      <c r="I53" s="88"/>
+      <c r="J53" s="88"/>
+      <c r="K53" s="88"/>
+      <c r="L53" s="88"/>
+      <c r="M53" s="88"/>
+      <c r="N53" s="88"/>
+      <c r="O53" s="88"/>
+      <c r="P53" s="88"/>
+      <c r="Q53" s="89"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
       <c r="U53" s="83"/>
+      <c r="V53" s="9"/>
+      <c r="W53" s="9"/>
+      <c r="X53" s="9"/>
+      <c r="Y53" s="9"/>
+      <c r="Z53" s="9"/>
+      <c r="AA53" s="9"/>
+      <c r="AB53" s="9"/>
+      <c r="AC53" s="9"/>
+      <c r="AD53" s="9"/>
+      <c r="AE53" s="9"/>
+      <c r="AF53" s="9"/>
+      <c r="AG53" s="9"/>
+      <c r="AH53" s="9"/>
       <c r="AI53" s="85"/>
-      <c r="AJ53" s="92"/>
+      <c r="AJ53" s="91"/>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
       <c r="AM53" s="61"/>
-      <c r="AN53" s="91"/>
-      <c r="AO53" s="91"/>
-      <c r="AP53" s="91"/>
-      <c r="AQ53" s="91"/>
-      <c r="AR53" s="91"/>
-      <c r="AS53" s="91"/>
-      <c r="AT53" s="91"/>
-      <c r="AU53" s="91"/>
-      <c r="AV53" s="91"/>
-      <c r="AW53" s="91"/>
-      <c r="AX53" s="91"/>
-      <c r="AY53" s="91"/>
-      <c r="AZ53" s="91"/>
-      <c r="BA53" s="90"/>
+      <c r="AN53" s="90"/>
+      <c r="AO53" s="90"/>
+      <c r="AP53" s="90"/>
+      <c r="AQ53" s="90"/>
+      <c r="AR53" s="90"/>
+      <c r="AS53" s="90"/>
+      <c r="AT53" s="90"/>
+      <c r="AU53" s="90"/>
+      <c r="AV53" s="90"/>
+      <c r="AW53" s="90"/>
+      <c r="AX53" s="90"/>
+      <c r="AY53" s="90"/>
+      <c r="AZ53" s="90"/>
+      <c r="BA53" s="89"/>
       <c r="BB53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9949,21 +10218,21 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="2"/>
-      <c r="U54" s="93"/>
-      <c r="V54" s="93"/>
-      <c r="W54" s="93"/>
-      <c r="X54" s="93"/>
-      <c r="Y54" s="93"/>
-      <c r="Z54" s="93"/>
-      <c r="AA54" s="93"/>
-      <c r="AB54" s="93"/>
-      <c r="AC54" s="93"/>
-      <c r="AD54" s="93"/>
-      <c r="AE54" s="93"/>
-      <c r="AF54" s="93"/>
-      <c r="AG54" s="93"/>
-      <c r="AH54" s="93"/>
-      <c r="AI54" s="93"/>
+      <c r="U54" s="92"/>
+      <c r="V54" s="92"/>
+      <c r="W54" s="92"/>
+      <c r="X54" s="92"/>
+      <c r="Y54" s="92"/>
+      <c r="Z54" s="92"/>
+      <c r="AA54" s="92"/>
+      <c r="AB54" s="92"/>
+      <c r="AC54" s="92"/>
+      <c r="AD54" s="92"/>
+      <c r="AE54" s="92"/>
+      <c r="AF54" s="92"/>
+      <c r="AG54" s="92"/>
+      <c r="AH54" s="92"/>
+      <c r="AI54" s="92"/>
       <c r="AJ54" s="2"/>
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
@@ -10127,8 +10396,8 @@
     <mergeCell ref="AN53:AZ53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.075" right="0.201388888888889" top="0.177777777777778" bottom="0.177777777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
